--- a/backend/PDF_DOC/EXCHANGE_RATES/Exchange Rates.xlsx
+++ b/backend/PDF_DOC/EXCHANGE_RATES/Exchange Rates.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293CD131-A6D3-4727-A561-D81F066F8A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E95799-87B9-453A-9013-2C89C094FD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -462,7 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -517,20 +517,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -876,1211 +862,1209 @@
       <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="24">
+      <c r="A5" s="4">
         <v>46219</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="4">
         <v>46220</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="25">
-        <v>1</v>
-      </c>
-      <c r="H5" s="26">
+      <c r="F5" s="20"/>
+      <c r="G5" s="11">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>27</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5">
         <v>25.45</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="24">
+      <c r="A6" s="4">
         <v>46219</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="4">
         <v>46220</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="29" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="25">
-        <v>1</v>
-      </c>
-      <c r="H6" s="26">
+      <c r="F6" s="20"/>
+      <c r="G6" s="11">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>68.900000000000006</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6">
         <v>65.95</v>
       </c>
-      <c r="J6" s="28"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
+      <c r="A7" s="4">
         <v>46219</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="4">
         <v>46220</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="25">
-        <v>1</v>
-      </c>
-      <c r="H7" s="26">
+      <c r="F7" s="20"/>
+      <c r="G7" s="11">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>272.5</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7">
         <v>242.05</v>
       </c>
-      <c r="J7" s="28"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="24">
+      <c r="A8" s="4">
         <v>46219</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="4">
         <v>46220</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="25">
-        <v>1</v>
-      </c>
-      <c r="H8" s="26">
+      <c r="F8" s="20"/>
+      <c r="G8" s="11">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>69.7</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8">
         <v>67.45</v>
       </c>
-      <c r="J8" s="28"/>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="24">
+      <c r="A9" s="4">
         <v>46219</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="4">
         <v>46220</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25" t="s">
+      <c r="C9" s="4"/>
+      <c r="D9" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25">
-        <v>1</v>
-      </c>
-      <c r="H9" s="26">
+      <c r="F9" s="20"/>
+      <c r="G9" s="11">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <v>122.15</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9">
         <v>117</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="24">
+      <c r="A10" s="4">
         <v>46219</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="4">
         <v>46220</v>
       </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25" t="s">
+      <c r="C10" s="4"/>
+      <c r="D10" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="25">
-        <v>1</v>
-      </c>
-      <c r="H10" s="26">
+      <c r="F10" s="20"/>
+      <c r="G10" s="11">
+        <v>1</v>
+      </c>
+      <c r="H10">
         <v>14.45</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10">
         <v>14</v>
       </c>
-      <c r="J10" s="28"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
+      <c r="A11" s="4">
         <v>46219</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="4">
         <v>46220</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="25">
-        <v>1</v>
-      </c>
-      <c r="H11" s="26">
+      <c r="F11" s="20"/>
+      <c r="G11" s="11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>14.95</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11">
         <v>14.6</v>
       </c>
-      <c r="J11" s="28"/>
+      <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="24">
+      <c r="A12" s="4">
         <v>46219</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="4">
         <v>46220</v>
       </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="25">
-        <v>1</v>
-      </c>
-      <c r="H12" s="26">
+      <c r="F12" s="20"/>
+      <c r="G12" s="11">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>112.35</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12">
         <v>108.6</v>
       </c>
-      <c r="J12" s="28"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="24">
+      <c r="A13" s="4">
         <v>46219</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="4">
         <v>46220</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="25">
-        <v>1</v>
-      </c>
-      <c r="H13" s="26">
+      <c r="F13" s="20"/>
+      <c r="G13" s="11">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>132.44999999999999</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13">
         <v>128.30000000000001</v>
       </c>
-      <c r="J13" s="28"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="24">
+      <c r="A14" s="4">
         <v>46219</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="4">
         <v>46220</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="25">
-        <v>1</v>
-      </c>
-      <c r="H14" s="26">
+      <c r="F14" s="20"/>
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
+      <c r="H14">
         <v>12.45</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14">
         <v>12.15</v>
       </c>
-      <c r="J14" s="28"/>
+      <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="24">
+      <c r="A15" s="4">
         <v>46219</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="4">
         <v>46220</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="25">
+      <c r="F15" s="20"/>
+      <c r="G15" s="11">
         <v>100</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15">
         <v>60.35</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15">
         <v>58.5</v>
       </c>
-      <c r="J15" s="28"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="24">
+      <c r="A16" s="4">
         <v>46219</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="4">
         <v>46220</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="25" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="29"/>
-      <c r="G16" s="25">
+      <c r="F16" s="20"/>
+      <c r="G16" s="11">
         <v>100</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16">
         <v>6.7</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16">
         <v>6.3</v>
       </c>
-      <c r="J16" s="28"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="24">
+      <c r="A17" s="4">
         <v>46219</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="4">
         <v>46220</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="25" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="29"/>
-      <c r="G17" s="25">
-        <v>1</v>
-      </c>
-      <c r="H17" s="26">
+      <c r="F17" s="20"/>
+      <c r="G17" s="11">
+        <v>1</v>
+      </c>
+      <c r="H17">
         <v>321.10000000000002</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17">
         <v>302.05</v>
       </c>
-      <c r="J17" s="28"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="24">
+      <c r="A18" s="4">
         <v>46219</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="4">
         <v>46220</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25" t="s">
+      <c r="C18" s="4"/>
+      <c r="D18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="29"/>
-      <c r="G18" s="25">
-        <v>1</v>
-      </c>
-      <c r="H18" s="26">
+      <c r="F18" s="20"/>
+      <c r="G18" s="11">
+        <v>1</v>
+      </c>
+      <c r="H18">
         <v>10.1</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18">
         <v>9.85</v>
       </c>
-      <c r="J18" s="28"/>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="24">
+      <c r="A19" s="4">
         <v>46219</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="4">
         <v>46220</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="4"/>
+      <c r="D19" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="25">
-        <v>1</v>
-      </c>
-      <c r="H19" s="26">
+      <c r="F19" s="20"/>
+      <c r="G19" s="11">
+        <v>1</v>
+      </c>
+      <c r="H19">
         <v>57.75</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19">
         <v>54.95</v>
       </c>
-      <c r="J19" s="28"/>
+      <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="24">
+      <c r="A20" s="4">
         <v>46219</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="4">
         <v>46220</v>
       </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="25" t="s">
+      <c r="C20" s="4"/>
+      <c r="D20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="29"/>
-      <c r="G20" s="25">
-        <v>1</v>
-      </c>
-      <c r="H20" s="26">
+      <c r="F20" s="20"/>
+      <c r="G20" s="11">
+        <v>1</v>
+      </c>
+      <c r="H20">
         <v>28.35</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20">
         <v>24.9</v>
       </c>
-      <c r="J20" s="28"/>
+      <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="24">
+      <c r="A21" s="4">
         <v>46219</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="4">
         <v>46220</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="25" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="29"/>
-      <c r="G21" s="25">
-        <v>1</v>
-      </c>
-      <c r="H21" s="26">
+      <c r="F21" s="20"/>
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <v>27.25</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I21">
         <v>24.3</v>
       </c>
-      <c r="J21" s="28"/>
+      <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="24">
+      <c r="A22" s="4">
         <v>46219</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="4">
         <v>46220</v>
       </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25" t="s">
+      <c r="C22" s="4"/>
+      <c r="D22" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="29"/>
-      <c r="G22" s="25">
-        <v>1</v>
-      </c>
-      <c r="H22" s="26">
+      <c r="F22" s="20"/>
+      <c r="G22" s="11">
+        <v>1</v>
+      </c>
+      <c r="H22">
         <v>10.15</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22">
         <v>9.9</v>
       </c>
-      <c r="J22" s="28"/>
+      <c r="J22" s="5"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="24">
+      <c r="A23" s="4">
         <v>46219</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="4">
         <v>46220</v>
       </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="25" t="s">
+      <c r="C23" s="4"/>
+      <c r="D23" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="25">
-        <v>1</v>
-      </c>
-      <c r="H23" s="26">
+      <c r="F23" s="20"/>
+      <c r="G23" s="11">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>76</v>
       </c>
-      <c r="I23" s="26">
+      <c r="I23">
         <v>73.5</v>
       </c>
-      <c r="J23" s="28"/>
+      <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="24">
+      <c r="A24" s="4">
         <v>46219</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="4">
         <v>46220</v>
       </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="29"/>
-      <c r="G24" s="25">
-        <v>1</v>
-      </c>
-      <c r="H24" s="26">
+      <c r="F24" s="20"/>
+      <c r="G24" s="11">
+        <v>1</v>
+      </c>
+      <c r="H24">
         <v>2.1</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24">
         <v>2</v>
       </c>
-      <c r="J24" s="28"/>
+      <c r="J24" s="5"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="24">
+      <c r="A25" s="4">
         <v>46219</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="4">
         <v>46220</v>
       </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="25" t="s">
+      <c r="C25" s="4"/>
+      <c r="D25" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="29"/>
-      <c r="G25" s="25">
-        <v>1</v>
-      </c>
-      <c r="H25" s="26">
+      <c r="F25" s="20"/>
+      <c r="G25" s="11">
+        <v>1</v>
+      </c>
+      <c r="H25">
         <v>97.2</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I25">
         <v>95.45</v>
       </c>
-      <c r="J25" s="28"/>
+      <c r="J25" s="5"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="24">
+      <c r="A26" s="4">
         <v>46219</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="4">
         <v>46220</v>
       </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="25">
-        <v>1</v>
-      </c>
-      <c r="H26" s="26">
+      <c r="F26" s="20"/>
+      <c r="G26" s="11">
+        <v>1</v>
+      </c>
+      <c r="H26">
         <v>6.05</v>
       </c>
-      <c r="I26" s="26">
+      <c r="I26">
         <v>5.75</v>
       </c>
-      <c r="J26" s="28"/>
+      <c r="J26" s="5"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="24">
+      <c r="A28" s="4">
         <v>46218</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="4">
         <v>46219</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="4">
         <v>46219</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25">
-        <v>1</v>
-      </c>
-      <c r="H28" s="26">
+      <c r="F28" s="11"/>
+      <c r="G28" s="11">
+        <v>1</v>
+      </c>
+      <c r="H28">
         <v>26.45</v>
       </c>
-      <c r="I28" s="26">
+      <c r="I28">
         <v>24.95</v>
       </c>
-      <c r="J28" s="27" t="s">
+      <c r="J28" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="24">
+      <c r="A29" s="4">
         <v>46218</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="4">
         <v>46219</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="4">
         <v>46219</v>
       </c>
-      <c r="D29" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="25" t="s">
+      <c r="D29" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25">
-        <v>1</v>
-      </c>
-      <c r="H29" s="26">
+      <c r="F29" s="11"/>
+      <c r="G29" s="11">
+        <v>1</v>
+      </c>
+      <c r="H29">
         <v>66.5</v>
       </c>
-      <c r="I29" s="26">
+      <c r="I29">
         <v>63.6</v>
       </c>
-      <c r="J29" s="28"/>
+      <c r="J29" s="5"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="24">
+      <c r="A30" s="4">
         <v>46218</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="4">
         <v>46219</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="4">
         <v>46219</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="E30" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25">
-        <v>1</v>
-      </c>
-      <c r="H30" s="26">
+      <c r="F30" s="11"/>
+      <c r="G30" s="11">
+        <v>1</v>
+      </c>
+      <c r="H30">
         <v>266.2</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30">
         <v>236.3</v>
       </c>
-      <c r="J30" s="28"/>
+      <c r="J30" s="5"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="24">
+      <c r="A31" s="4">
         <v>46218</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="4">
         <v>46219</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="4">
         <v>46219</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25">
-        <v>1</v>
-      </c>
-      <c r="H31" s="26">
+      <c r="F31" s="11"/>
+      <c r="G31" s="11">
+        <v>1</v>
+      </c>
+      <c r="H31">
         <v>67.400000000000006</v>
       </c>
-      <c r="I31" s="26">
+      <c r="I31">
         <v>65.2</v>
       </c>
-      <c r="J31" s="28"/>
+      <c r="J31" s="5"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="24">
+      <c r="A32" s="4">
         <v>46218</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="4">
         <v>46219</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="4">
         <v>46219</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="E32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25">
-        <v>1</v>
-      </c>
-      <c r="H32" s="26">
+      <c r="F32" s="11"/>
+      <c r="G32" s="11">
+        <v>1</v>
+      </c>
+      <c r="H32">
         <v>118.85</v>
       </c>
-      <c r="I32" s="26">
+      <c r="I32">
         <v>113.85</v>
       </c>
-      <c r="J32" s="28"/>
+      <c r="J32" s="5"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="24">
+      <c r="A33" s="4">
         <v>46218</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="4">
         <v>46219</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="4">
         <v>46219</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="E33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25">
-        <v>1</v>
-      </c>
-      <c r="H33" s="26">
+      <c r="F33" s="11"/>
+      <c r="G33" s="11">
+        <v>1</v>
+      </c>
+      <c r="H33">
         <v>14.15</v>
       </c>
-      <c r="I33" s="26">
+      <c r="I33">
         <v>13.65</v>
       </c>
-      <c r="J33" s="28"/>
+      <c r="J33" s="5"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="24">
+      <c r="A34" s="4">
         <v>46218</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="4">
         <v>46219</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="4">
         <v>46219</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="D34" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25">
-        <v>1</v>
-      </c>
-      <c r="H34" s="26">
+      <c r="F34" s="11"/>
+      <c r="G34" s="11">
+        <v>1</v>
+      </c>
+      <c r="H34">
         <v>14.55</v>
       </c>
-      <c r="I34" s="26">
+      <c r="I34">
         <v>14.15</v>
       </c>
-      <c r="J34" s="28"/>
+      <c r="J34" s="5"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="24">
+      <c r="A35" s="4">
         <v>46218</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="4">
         <v>46219</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="4">
         <v>46219</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E35" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25">
-        <v>1</v>
-      </c>
-      <c r="H35" s="26">
+      <c r="F35" s="11"/>
+      <c r="G35" s="11">
+        <v>1</v>
+      </c>
+      <c r="H35">
         <v>109.1</v>
       </c>
-      <c r="I35" s="26">
+      <c r="I35">
         <v>105.4</v>
       </c>
-      <c r="J35" s="28"/>
+      <c r="J35" s="5"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="24">
+      <c r="A36" s="4">
         <v>46218</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="4">
         <v>46219</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="4">
         <v>46219</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="E36" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25">
-        <v>1</v>
-      </c>
-      <c r="H36" s="26">
+      <c r="F36" s="11"/>
+      <c r="G36" s="11">
+        <v>1</v>
+      </c>
+      <c r="H36">
         <v>126.35</v>
       </c>
-      <c r="I36" s="26">
+      <c r="I36">
         <v>122.35</v>
       </c>
-      <c r="J36" s="28"/>
+      <c r="J36" s="5"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="24">
+      <c r="A37" s="4">
         <v>46218</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="4">
         <v>46219</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="4">
         <v>46219</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D37" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="E37" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25">
-        <v>1</v>
-      </c>
-      <c r="H37" s="26">
+      <c r="F37" s="11"/>
+      <c r="G37" s="11">
+        <v>1</v>
+      </c>
+      <c r="H37">
         <v>12.2</v>
       </c>
-      <c r="I37" s="26">
+      <c r="I37">
         <v>11.9</v>
       </c>
-      <c r="J37" s="28"/>
+      <c r="J37" s="5"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="24">
+      <c r="A38" s="4">
         <v>46218</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="4">
         <v>46219</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="4">
         <v>46219</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="D38" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="25" t="s">
+      <c r="E38" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25">
+      <c r="F38" s="11"/>
+      <c r="G38" s="11">
         <v>100</v>
       </c>
-      <c r="H38" s="26">
+      <c r="H38">
         <v>59.25</v>
       </c>
-      <c r="I38" s="26">
+      <c r="I38">
         <v>57.45</v>
       </c>
-      <c r="J38" s="28"/>
+      <c r="J38" s="5"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="24">
+      <c r="A39" s="4">
         <v>46218</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="4">
         <v>46219</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="4">
         <v>46219</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25">
+      <c r="F39" s="11"/>
+      <c r="G39" s="11">
         <v>100</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39">
         <v>6.65</v>
       </c>
-      <c r="I39" s="26">
+      <c r="I39">
         <v>6.3</v>
       </c>
-      <c r="J39" s="28"/>
+      <c r="J39" s="5"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="24">
+      <c r="A40" s="4">
         <v>46218</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="4">
         <v>46219</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="4">
         <v>46219</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="25" t="s">
+      <c r="E40" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25">
-        <v>1</v>
-      </c>
-      <c r="H40" s="26">
+      <c r="F40" s="11"/>
+      <c r="G40" s="11">
+        <v>1</v>
+      </c>
+      <c r="H40">
         <v>314.5</v>
       </c>
-      <c r="I40" s="26">
+      <c r="I40">
         <v>295.7</v>
       </c>
-      <c r="J40" s="28"/>
+      <c r="J40" s="5"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="24">
+      <c r="A41" s="4">
         <v>46218</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="4">
         <v>46219</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="4">
         <v>46219</v>
       </c>
-      <c r="D41" s="25" t="s">
+      <c r="D41" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="25" t="s">
+      <c r="E41" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25">
-        <v>1</v>
-      </c>
-      <c r="H41" s="26">
+      <c r="F41" s="11"/>
+      <c r="G41" s="11">
+        <v>1</v>
+      </c>
+      <c r="H41">
         <v>9.6999999999999993</v>
       </c>
-      <c r="I41" s="26">
+      <c r="I41">
         <v>9.4499999999999993</v>
       </c>
-      <c r="J41" s="28"/>
+      <c r="J41" s="5"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="24">
+      <c r="A42" s="4">
         <v>46218</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="4">
         <v>46219</v>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="4">
         <v>46219</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="25" t="s">
+      <c r="E42" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25">
-        <v>1</v>
-      </c>
-      <c r="H42" s="26">
+      <c r="F42" s="11"/>
+      <c r="G42" s="11">
+        <v>1</v>
+      </c>
+      <c r="H42">
         <v>57.3</v>
       </c>
-      <c r="I42" s="26">
+      <c r="I42">
         <v>54.55</v>
       </c>
-      <c r="J42" s="28"/>
+      <c r="J42" s="5"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="24">
+      <c r="A43" s="4">
         <v>46218</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B43" s="4">
         <v>46219</v>
       </c>
-      <c r="C43" s="24">
+      <c r="C43" s="4">
         <v>46219</v>
       </c>
-      <c r="D43" s="25" t="s">
+      <c r="D43" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="25" t="s">
+      <c r="E43" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25">
-        <v>1</v>
-      </c>
-      <c r="H43" s="26">
+      <c r="F43" s="11"/>
+      <c r="G43" s="11">
+        <v>1</v>
+      </c>
+      <c r="H43">
         <v>27.8</v>
       </c>
-      <c r="I43" s="26">
+      <c r="I43">
         <v>24.35</v>
       </c>
-      <c r="J43" s="28"/>
+      <c r="J43" s="5"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="24">
+      <c r="A44" s="4">
         <v>46218</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="4">
         <v>46219</v>
       </c>
-      <c r="C44" s="24">
+      <c r="C44" s="4">
         <v>46219</v>
       </c>
-      <c r="D44" s="25" t="s">
+      <c r="D44" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="25" t="s">
+      <c r="E44" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25">
-        <v>1</v>
-      </c>
-      <c r="H44" s="26">
+      <c r="F44" s="11"/>
+      <c r="G44" s="11">
+        <v>1</v>
+      </c>
+      <c r="H44">
         <v>26.75</v>
       </c>
-      <c r="I44" s="26">
+      <c r="I44">
         <v>23.85</v>
       </c>
-      <c r="J44" s="28"/>
+      <c r="J44" s="5"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="24">
+      <c r="A45" s="4">
         <v>46218</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B45" s="4">
         <v>46219</v>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="4">
         <v>46219</v>
       </c>
-      <c r="D45" s="25" t="s">
+      <c r="D45" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25">
-        <v>1</v>
-      </c>
-      <c r="H45" s="26">
+      <c r="F45" s="11"/>
+      <c r="G45" s="11">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I45" s="26">
+      <c r="I45">
         <v>9.5500000000000007</v>
       </c>
-      <c r="J45" s="28"/>
+      <c r="J45" s="5"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="24">
+      <c r="A46" s="4">
         <v>46218</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B46" s="4">
         <v>46219</v>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="4">
         <v>46219</v>
       </c>
-      <c r="D46" s="25" t="s">
+      <c r="D46" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E46" s="25" t="s">
+      <c r="E46" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25">
-        <v>1</v>
-      </c>
-      <c r="H46" s="26">
+      <c r="F46" s="11"/>
+      <c r="G46" s="11">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <v>74</v>
       </c>
-      <c r="I46" s="26">
+      <c r="I46">
         <v>71.55</v>
       </c>
-      <c r="J46" s="28"/>
+      <c r="J46" s="5"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="24">
+      <c r="A47" s="4">
         <v>46218</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B47" s="4">
         <v>46219</v>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="4">
         <v>46219</v>
       </c>
-      <c r="D47" s="25" t="s">
+      <c r="D47" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="25" t="s">
+      <c r="E47" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25">
-        <v>1</v>
-      </c>
-      <c r="H47" s="26">
+      <c r="F47" s="11"/>
+      <c r="G47" s="11">
+        <v>1</v>
+      </c>
+      <c r="H47">
         <v>2.1</v>
       </c>
-      <c r="I47" s="26">
+      <c r="I47">
         <v>1.95</v>
       </c>
-      <c r="J47" s="28"/>
+      <c r="J47" s="5"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="24">
+      <c r="A48" s="4">
         <v>46218</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B48" s="4">
         <v>46219</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="4">
         <v>46219</v>
       </c>
-      <c r="D48" s="25" t="s">
+      <c r="D48" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="25" t="s">
+      <c r="E48" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25">
-        <v>1</v>
-      </c>
-      <c r="H48" s="26">
+      <c r="F48" s="11"/>
+      <c r="G48" s="11">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <v>95.2</v>
       </c>
-      <c r="I48" s="26">
+      <c r="I48">
         <v>93.5</v>
       </c>
-      <c r="J48" s="28"/>
+      <c r="J48" s="5"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="24">
+      <c r="A49" s="4">
         <v>46218</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="4">
         <v>46219</v>
       </c>
-      <c r="C49" s="24">
+      <c r="C49" s="4">
         <v>46219</v>
       </c>
-      <c r="D49" s="25" t="s">
+      <c r="D49" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="25" t="s">
+      <c r="E49" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25">
-        <v>1</v>
-      </c>
-      <c r="H49" s="26">
+      <c r="F49" s="11"/>
+      <c r="G49" s="11">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <v>5.85</v>
       </c>
-      <c r="I49" s="26">
+      <c r="I49">
         <v>5.55</v>
       </c>
-      <c r="J49" s="28"/>
+      <c r="J49" s="5"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="24"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="28"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="J50" s="5"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
@@ -2089,7 +2073,7 @@
       <c r="B51" s="4">
         <v>46218</v>
       </c>
-      <c r="C51" s="24">
+      <c r="C51" s="4">
         <v>46218</v>
       </c>
       <c r="D51" s="11" t="s">
@@ -2119,7 +2103,7 @@
       <c r="B52" s="4">
         <v>46218</v>
       </c>
-      <c r="C52" s="24">
+      <c r="C52" s="4">
         <v>46218</v>
       </c>
       <c r="D52" s="11" t="s">
@@ -2147,7 +2131,7 @@
       <c r="B53" s="4">
         <v>46218</v>
       </c>
-      <c r="C53" s="24">
+      <c r="C53" s="4">
         <v>46218</v>
       </c>
       <c r="D53" s="11" t="s">
@@ -2175,7 +2159,7 @@
       <c r="B54" s="4">
         <v>46218</v>
       </c>
-      <c r="C54" s="24">
+      <c r="C54" s="4">
         <v>46218</v>
       </c>
       <c r="D54" s="11" t="s">
@@ -2203,7 +2187,7 @@
       <c r="B55" s="4">
         <v>46218</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C55" s="4">
         <v>46218</v>
       </c>
       <c r="D55" s="11" t="s">
@@ -2231,7 +2215,7 @@
       <c r="B56" s="4">
         <v>46218</v>
       </c>
-      <c r="C56" s="24">
+      <c r="C56" s="4">
         <v>46218</v>
       </c>
       <c r="D56" s="11" t="s">
@@ -2259,7 +2243,7 @@
       <c r="B57" s="4">
         <v>46218</v>
       </c>
-      <c r="C57" s="24">
+      <c r="C57" s="4">
         <v>46218</v>
       </c>
       <c r="D57" s="11" t="s">
@@ -2287,7 +2271,7 @@
       <c r="B58" s="4">
         <v>46218</v>
       </c>
-      <c r="C58" s="24">
+      <c r="C58" s="4">
         <v>46218</v>
       </c>
       <c r="D58" s="11" t="s">
@@ -2315,7 +2299,7 @@
       <c r="B59" s="4">
         <v>46218</v>
       </c>
-      <c r="C59" s="24">
+      <c r="C59" s="4">
         <v>46218</v>
       </c>
       <c r="D59" s="11" t="s">
@@ -2343,7 +2327,7 @@
       <c r="B60" s="4">
         <v>46218</v>
       </c>
-      <c r="C60" s="24">
+      <c r="C60" s="4">
         <v>46218</v>
       </c>
       <c r="D60" s="11" t="s">
@@ -2371,7 +2355,7 @@
       <c r="B61" s="4">
         <v>46218</v>
       </c>
-      <c r="C61" s="24">
+      <c r="C61" s="4">
         <v>46218</v>
       </c>
       <c r="D61" s="11" t="s">
@@ -2399,7 +2383,7 @@
       <c r="B62" s="4">
         <v>46218</v>
       </c>
-      <c r="C62" s="24">
+      <c r="C62" s="4">
         <v>46218</v>
       </c>
       <c r="D62" s="11" t="s">
@@ -2427,7 +2411,7 @@
       <c r="B63" s="4">
         <v>46218</v>
       </c>
-      <c r="C63" s="24">
+      <c r="C63" s="4">
         <v>46218</v>
       </c>
       <c r="D63" s="11" t="s">
@@ -2455,7 +2439,7 @@
       <c r="B64" s="4">
         <v>46218</v>
       </c>
-      <c r="C64" s="24">
+      <c r="C64" s="4">
         <v>46218</v>
       </c>
       <c r="D64" s="11" t="s">
@@ -2483,7 +2467,7 @@
       <c r="B65" s="4">
         <v>46218</v>
       </c>
-      <c r="C65" s="24">
+      <c r="C65" s="4">
         <v>46218</v>
       </c>
       <c r="D65" s="11" t="s">
@@ -2511,7 +2495,7 @@
       <c r="B66" s="4">
         <v>46218</v>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="4">
         <v>46218</v>
       </c>
       <c r="D66" s="11" t="s">
@@ -2539,7 +2523,7 @@
       <c r="B67" s="4">
         <v>46218</v>
       </c>
-      <c r="C67" s="24">
+      <c r="C67" s="4">
         <v>46218</v>
       </c>
       <c r="D67" s="11" t="s">
@@ -2567,7 +2551,7 @@
       <c r="B68" s="4">
         <v>46218</v>
       </c>
-      <c r="C68" s="24">
+      <c r="C68" s="4">
         <v>46218</v>
       </c>
       <c r="D68" s="11" t="s">
@@ -2595,7 +2579,7 @@
       <c r="B69" s="4">
         <v>46218</v>
       </c>
-      <c r="C69" s="24">
+      <c r="C69" s="4">
         <v>46218</v>
       </c>
       <c r="D69" s="11" t="s">
@@ -2623,7 +2607,7 @@
       <c r="B70" s="4">
         <v>46218</v>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="4">
         <v>46218</v>
       </c>
       <c r="D70" s="11" t="s">
@@ -2651,7 +2635,7 @@
       <c r="B71" s="4">
         <v>46218</v>
       </c>
-      <c r="C71" s="24">
+      <c r="C71" s="4">
         <v>46218</v>
       </c>
       <c r="D71" s="11" t="s">
@@ -2679,7 +2663,7 @@
       <c r="B72" s="4">
         <v>46218</v>
       </c>
-      <c r="C72" s="24">
+      <c r="C72" s="4">
         <v>46218</v>
       </c>
       <c r="D72" s="11" t="s">
@@ -41678,138 +41662,1273 @@
     </row>
   </sheetData>
   <mergeCells count="1431">
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="E178:F178"/>
-    <mergeCell ref="E179:F179"/>
-    <mergeCell ref="E180:F180"/>
-    <mergeCell ref="E181:F181"/>
-    <mergeCell ref="E182:F182"/>
-    <mergeCell ref="E183:F183"/>
-    <mergeCell ref="E184:F184"/>
-    <mergeCell ref="E185:F185"/>
-    <mergeCell ref="E186:F186"/>
-    <mergeCell ref="E187:F187"/>
-    <mergeCell ref="E160:F160"/>
-    <mergeCell ref="E161:F161"/>
-    <mergeCell ref="E162:F162"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="E164:F164"/>
-    <mergeCell ref="E166:F166"/>
-    <mergeCell ref="E167:F167"/>
-    <mergeCell ref="E168:F168"/>
-    <mergeCell ref="E169:F169"/>
-    <mergeCell ref="E170:F170"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="E173:F173"/>
-    <mergeCell ref="E174:F174"/>
-    <mergeCell ref="E175:F175"/>
-    <mergeCell ref="E176:F176"/>
-    <mergeCell ref="E177:F177"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="E146:F146"/>
-    <mergeCell ref="E147:F147"/>
-    <mergeCell ref="E148:F148"/>
-    <mergeCell ref="E149:F149"/>
-    <mergeCell ref="E150:F150"/>
-    <mergeCell ref="E151:F151"/>
-    <mergeCell ref="E152:F152"/>
-    <mergeCell ref="E153:F153"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="E155:F155"/>
-    <mergeCell ref="E156:F156"/>
-    <mergeCell ref="E157:F157"/>
-    <mergeCell ref="E158:F158"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="E206:F206"/>
-    <mergeCell ref="E207:F207"/>
-    <mergeCell ref="E208:F208"/>
-    <mergeCell ref="E209:F209"/>
-    <mergeCell ref="E210:F210"/>
-    <mergeCell ref="E189:F189"/>
-    <mergeCell ref="E190:F190"/>
-    <mergeCell ref="E191:F191"/>
-    <mergeCell ref="E192:F192"/>
-    <mergeCell ref="E193:F193"/>
-    <mergeCell ref="E194:F194"/>
-    <mergeCell ref="E195:F195"/>
-    <mergeCell ref="E196:F196"/>
-    <mergeCell ref="E197:F197"/>
-    <mergeCell ref="E198:F198"/>
-    <mergeCell ref="E199:F199"/>
-    <mergeCell ref="E200:F200"/>
-    <mergeCell ref="E201:F201"/>
-    <mergeCell ref="E202:F202"/>
-    <mergeCell ref="E203:F203"/>
-    <mergeCell ref="E204:F204"/>
-    <mergeCell ref="E205:F205"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="E298:F298"/>
+    <mergeCell ref="E299:F299"/>
+    <mergeCell ref="E300:F300"/>
+    <mergeCell ref="E301:F301"/>
+    <mergeCell ref="E302:F302"/>
+    <mergeCell ref="E281:F281"/>
+    <mergeCell ref="E282:F282"/>
+    <mergeCell ref="E283:F283"/>
+    <mergeCell ref="E284:F284"/>
+    <mergeCell ref="E285:F285"/>
+    <mergeCell ref="E286:F286"/>
+    <mergeCell ref="E287:F287"/>
+    <mergeCell ref="E288:F288"/>
+    <mergeCell ref="E289:F289"/>
+    <mergeCell ref="E290:F290"/>
+    <mergeCell ref="E291:F291"/>
+    <mergeCell ref="E292:F292"/>
+    <mergeCell ref="E293:F293"/>
+    <mergeCell ref="E294:F294"/>
+    <mergeCell ref="E295:F295"/>
+    <mergeCell ref="E296:F296"/>
+    <mergeCell ref="E297:F297"/>
+    <mergeCell ref="E434:F434"/>
+    <mergeCell ref="E435:F435"/>
+    <mergeCell ref="E436:F436"/>
+    <mergeCell ref="E437:F437"/>
+    <mergeCell ref="E438:F438"/>
+    <mergeCell ref="E439:F439"/>
+    <mergeCell ref="E440:F440"/>
+    <mergeCell ref="E453:F453"/>
+    <mergeCell ref="E454:F454"/>
+    <mergeCell ref="E455:F455"/>
+    <mergeCell ref="E456:F456"/>
+    <mergeCell ref="E457:F457"/>
+    <mergeCell ref="E458:F458"/>
+    <mergeCell ref="E447:F447"/>
+    <mergeCell ref="E448:F448"/>
+    <mergeCell ref="E449:F449"/>
+    <mergeCell ref="E450:F450"/>
+    <mergeCell ref="E451:F451"/>
+    <mergeCell ref="E452:F452"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E442:F442"/>
+    <mergeCell ref="E443:F443"/>
+    <mergeCell ref="E444:F444"/>
+    <mergeCell ref="E445:F445"/>
+    <mergeCell ref="E446:F446"/>
+    <mergeCell ref="E419:F419"/>
+    <mergeCell ref="E420:F420"/>
+    <mergeCell ref="E421:F421"/>
+    <mergeCell ref="E422:F422"/>
+    <mergeCell ref="E423:F423"/>
+    <mergeCell ref="E424:F424"/>
+    <mergeCell ref="E425:F425"/>
+    <mergeCell ref="E426:F426"/>
+    <mergeCell ref="E427:F427"/>
+    <mergeCell ref="E428:F428"/>
+    <mergeCell ref="E429:F429"/>
+    <mergeCell ref="E430:F430"/>
+    <mergeCell ref="E431:F431"/>
+    <mergeCell ref="E432:F432"/>
+    <mergeCell ref="E397:F397"/>
+    <mergeCell ref="E399:F399"/>
+    <mergeCell ref="E401:F401"/>
+    <mergeCell ref="E403:F403"/>
+    <mergeCell ref="E405:F405"/>
+    <mergeCell ref="E407:F407"/>
+    <mergeCell ref="E409:F409"/>
+    <mergeCell ref="E411:F411"/>
+    <mergeCell ref="E413:F413"/>
+    <mergeCell ref="E415:F415"/>
+    <mergeCell ref="E417:F417"/>
+    <mergeCell ref="E433:F433"/>
+    <mergeCell ref="E472:F472"/>
+    <mergeCell ref="E473:F473"/>
+    <mergeCell ref="E474:F474"/>
+    <mergeCell ref="E475:F475"/>
+    <mergeCell ref="E476:F476"/>
+    <mergeCell ref="E477:F477"/>
+    <mergeCell ref="E466:F466"/>
+    <mergeCell ref="E467:F467"/>
+    <mergeCell ref="E468:F468"/>
+    <mergeCell ref="E469:F469"/>
+    <mergeCell ref="E470:F470"/>
+    <mergeCell ref="E471:F471"/>
+    <mergeCell ref="E459:F459"/>
+    <mergeCell ref="E460:F460"/>
+    <mergeCell ref="E461:F461"/>
+    <mergeCell ref="E462:F462"/>
+    <mergeCell ref="E463:F463"/>
+    <mergeCell ref="E465:F465"/>
+    <mergeCell ref="E491:F491"/>
+    <mergeCell ref="E492:F492"/>
+    <mergeCell ref="E493:F493"/>
+    <mergeCell ref="E494:F494"/>
+    <mergeCell ref="E495:F495"/>
+    <mergeCell ref="E496:F496"/>
+    <mergeCell ref="E484:F484"/>
+    <mergeCell ref="E485:F485"/>
+    <mergeCell ref="E486:F486"/>
+    <mergeCell ref="E488:F488"/>
+    <mergeCell ref="E489:F489"/>
+    <mergeCell ref="E490:F490"/>
+    <mergeCell ref="E478:F478"/>
+    <mergeCell ref="E479:F479"/>
+    <mergeCell ref="E480:F480"/>
+    <mergeCell ref="E481:F481"/>
+    <mergeCell ref="E482:F482"/>
+    <mergeCell ref="E483:F483"/>
+    <mergeCell ref="E509:F509"/>
+    <mergeCell ref="E511:F511"/>
+    <mergeCell ref="E512:F512"/>
+    <mergeCell ref="E513:F513"/>
+    <mergeCell ref="E514:F514"/>
+    <mergeCell ref="E515:F515"/>
+    <mergeCell ref="E503:F503"/>
+    <mergeCell ref="E504:F504"/>
+    <mergeCell ref="E505:F505"/>
+    <mergeCell ref="E506:F506"/>
+    <mergeCell ref="E507:F507"/>
+    <mergeCell ref="E508:F508"/>
+    <mergeCell ref="E497:F497"/>
+    <mergeCell ref="E498:F498"/>
+    <mergeCell ref="E499:F499"/>
+    <mergeCell ref="E500:F500"/>
+    <mergeCell ref="E501:F501"/>
+    <mergeCell ref="E502:F502"/>
+    <mergeCell ref="E528:F528"/>
+    <mergeCell ref="E529:F529"/>
+    <mergeCell ref="E530:F530"/>
+    <mergeCell ref="E531:F531"/>
+    <mergeCell ref="E532:F532"/>
+    <mergeCell ref="E534:F534"/>
+    <mergeCell ref="E522:F522"/>
+    <mergeCell ref="E523:F523"/>
+    <mergeCell ref="E524:F524"/>
+    <mergeCell ref="E525:F525"/>
+    <mergeCell ref="E526:F526"/>
+    <mergeCell ref="E527:F527"/>
+    <mergeCell ref="E516:F516"/>
+    <mergeCell ref="E517:F517"/>
+    <mergeCell ref="E518:F518"/>
+    <mergeCell ref="E519:F519"/>
+    <mergeCell ref="E520:F520"/>
+    <mergeCell ref="E521:F521"/>
+    <mergeCell ref="E547:F547"/>
+    <mergeCell ref="E548:F548"/>
+    <mergeCell ref="E549:F549"/>
+    <mergeCell ref="E550:F550"/>
+    <mergeCell ref="E551:F551"/>
+    <mergeCell ref="E552:F552"/>
+    <mergeCell ref="E541:F541"/>
+    <mergeCell ref="E542:F542"/>
+    <mergeCell ref="E543:F543"/>
+    <mergeCell ref="E544:F544"/>
+    <mergeCell ref="E545:F545"/>
+    <mergeCell ref="E546:F546"/>
+    <mergeCell ref="E535:F535"/>
+    <mergeCell ref="E536:F536"/>
+    <mergeCell ref="E537:F537"/>
+    <mergeCell ref="E538:F538"/>
+    <mergeCell ref="E539:F539"/>
+    <mergeCell ref="E540:F540"/>
+    <mergeCell ref="E565:F565"/>
+    <mergeCell ref="E566:F566"/>
+    <mergeCell ref="E567:F567"/>
+    <mergeCell ref="E568:F568"/>
+    <mergeCell ref="E569:F569"/>
+    <mergeCell ref="E570:F570"/>
+    <mergeCell ref="E559:F559"/>
+    <mergeCell ref="E560:F560"/>
+    <mergeCell ref="E561:F561"/>
+    <mergeCell ref="E562:F562"/>
+    <mergeCell ref="E563:F563"/>
+    <mergeCell ref="E564:F564"/>
+    <mergeCell ref="E553:F553"/>
+    <mergeCell ref="E554:F554"/>
+    <mergeCell ref="E555:F555"/>
+    <mergeCell ref="E557:F557"/>
+    <mergeCell ref="E558:F558"/>
+    <mergeCell ref="E584:F584"/>
+    <mergeCell ref="E585:F585"/>
+    <mergeCell ref="E586:F586"/>
+    <mergeCell ref="E587:F587"/>
+    <mergeCell ref="E588:F588"/>
+    <mergeCell ref="E589:F589"/>
+    <mergeCell ref="E577:F577"/>
+    <mergeCell ref="E578:F578"/>
+    <mergeCell ref="E580:F580"/>
+    <mergeCell ref="E581:F581"/>
+    <mergeCell ref="E582:F582"/>
+    <mergeCell ref="E583:F583"/>
+    <mergeCell ref="E571:F571"/>
+    <mergeCell ref="E572:F572"/>
+    <mergeCell ref="E573:F573"/>
+    <mergeCell ref="E574:F574"/>
+    <mergeCell ref="E575:F575"/>
+    <mergeCell ref="E576:F576"/>
+    <mergeCell ref="E603:F603"/>
+    <mergeCell ref="E604:F604"/>
+    <mergeCell ref="E605:F605"/>
+    <mergeCell ref="E606:F606"/>
+    <mergeCell ref="E607:F607"/>
+    <mergeCell ref="E608:F608"/>
+    <mergeCell ref="E596:F596"/>
+    <mergeCell ref="E597:F597"/>
+    <mergeCell ref="E598:F598"/>
+    <mergeCell ref="E599:F599"/>
+    <mergeCell ref="E600:F600"/>
+    <mergeCell ref="E601:F601"/>
+    <mergeCell ref="E590:F590"/>
+    <mergeCell ref="E591:F591"/>
+    <mergeCell ref="E592:F592"/>
+    <mergeCell ref="E593:F593"/>
+    <mergeCell ref="E594:F594"/>
+    <mergeCell ref="E595:F595"/>
+    <mergeCell ref="E621:F621"/>
+    <mergeCell ref="E622:F622"/>
+    <mergeCell ref="E623:F623"/>
+    <mergeCell ref="E624:F624"/>
+    <mergeCell ref="E626:F626"/>
+    <mergeCell ref="E627:F627"/>
+    <mergeCell ref="E615:F615"/>
+    <mergeCell ref="E616:F616"/>
+    <mergeCell ref="E617:F617"/>
+    <mergeCell ref="E618:F618"/>
+    <mergeCell ref="E619:F619"/>
+    <mergeCell ref="E620:F620"/>
+    <mergeCell ref="E609:F609"/>
+    <mergeCell ref="E610:F610"/>
+    <mergeCell ref="E611:F611"/>
+    <mergeCell ref="E612:F612"/>
+    <mergeCell ref="E613:F613"/>
+    <mergeCell ref="E614:F614"/>
+    <mergeCell ref="E640:F640"/>
+    <mergeCell ref="E641:F641"/>
+    <mergeCell ref="E642:F642"/>
+    <mergeCell ref="E643:F643"/>
+    <mergeCell ref="E644:F644"/>
+    <mergeCell ref="E645:F645"/>
+    <mergeCell ref="E634:F634"/>
+    <mergeCell ref="E635:F635"/>
+    <mergeCell ref="E636:F636"/>
+    <mergeCell ref="E637:F637"/>
+    <mergeCell ref="E638:F638"/>
+    <mergeCell ref="E639:F639"/>
+    <mergeCell ref="E628:F628"/>
+    <mergeCell ref="E629:F629"/>
+    <mergeCell ref="E630:F630"/>
+    <mergeCell ref="E631:F631"/>
+    <mergeCell ref="E632:F632"/>
+    <mergeCell ref="E633:F633"/>
+    <mergeCell ref="E659:F659"/>
+    <mergeCell ref="E660:F660"/>
+    <mergeCell ref="E661:F661"/>
+    <mergeCell ref="E662:F662"/>
+    <mergeCell ref="E663:F663"/>
+    <mergeCell ref="E664:F664"/>
+    <mergeCell ref="E653:F653"/>
+    <mergeCell ref="E654:F654"/>
+    <mergeCell ref="E655:F655"/>
+    <mergeCell ref="E656:F656"/>
+    <mergeCell ref="E657:F657"/>
+    <mergeCell ref="E658:F658"/>
+    <mergeCell ref="E646:F646"/>
+    <mergeCell ref="E647:F647"/>
+    <mergeCell ref="E649:F649"/>
+    <mergeCell ref="E650:F650"/>
+    <mergeCell ref="E651:F651"/>
+    <mergeCell ref="E652:F652"/>
+    <mergeCell ref="E678:F678"/>
+    <mergeCell ref="E679:F679"/>
+    <mergeCell ref="E680:F680"/>
+    <mergeCell ref="E681:F681"/>
+    <mergeCell ref="E682:F682"/>
+    <mergeCell ref="E683:F683"/>
+    <mergeCell ref="E672:F672"/>
+    <mergeCell ref="E673:F673"/>
+    <mergeCell ref="E674:F674"/>
+    <mergeCell ref="E675:F675"/>
+    <mergeCell ref="E676:F676"/>
+    <mergeCell ref="E677:F677"/>
+    <mergeCell ref="E665:F665"/>
+    <mergeCell ref="E666:F666"/>
+    <mergeCell ref="E667:F667"/>
+    <mergeCell ref="E668:F668"/>
+    <mergeCell ref="E669:F669"/>
+    <mergeCell ref="E670:F670"/>
+    <mergeCell ref="E697:F697"/>
+    <mergeCell ref="E698:F698"/>
+    <mergeCell ref="E699:F699"/>
+    <mergeCell ref="E700:F700"/>
+    <mergeCell ref="E701:F701"/>
+    <mergeCell ref="E702:F702"/>
+    <mergeCell ref="E690:F690"/>
+    <mergeCell ref="E691:F691"/>
+    <mergeCell ref="E692:F692"/>
+    <mergeCell ref="E693:F693"/>
+    <mergeCell ref="E695:F695"/>
+    <mergeCell ref="E696:F696"/>
+    <mergeCell ref="E684:F684"/>
+    <mergeCell ref="E685:F685"/>
+    <mergeCell ref="E686:F686"/>
+    <mergeCell ref="E687:F687"/>
+    <mergeCell ref="E688:F688"/>
+    <mergeCell ref="E689:F689"/>
+    <mergeCell ref="E715:F715"/>
+    <mergeCell ref="E716:F716"/>
+    <mergeCell ref="E718:F718"/>
+    <mergeCell ref="E719:F719"/>
+    <mergeCell ref="E720:F720"/>
+    <mergeCell ref="E721:F721"/>
+    <mergeCell ref="E709:F709"/>
+    <mergeCell ref="E710:F710"/>
+    <mergeCell ref="E711:F711"/>
+    <mergeCell ref="E712:F712"/>
+    <mergeCell ref="E713:F713"/>
+    <mergeCell ref="E714:F714"/>
+    <mergeCell ref="E703:F703"/>
+    <mergeCell ref="E704:F704"/>
+    <mergeCell ref="E705:F705"/>
+    <mergeCell ref="E706:F706"/>
+    <mergeCell ref="E707:F707"/>
+    <mergeCell ref="E708:F708"/>
+    <mergeCell ref="E734:F734"/>
+    <mergeCell ref="E735:F735"/>
+    <mergeCell ref="E736:F736"/>
+    <mergeCell ref="E737:F737"/>
+    <mergeCell ref="E738:F738"/>
+    <mergeCell ref="E739:F739"/>
+    <mergeCell ref="E728:F728"/>
+    <mergeCell ref="E729:F729"/>
+    <mergeCell ref="E730:F730"/>
+    <mergeCell ref="E731:F731"/>
+    <mergeCell ref="E732:F732"/>
+    <mergeCell ref="E733:F733"/>
+    <mergeCell ref="E722:F722"/>
+    <mergeCell ref="E723:F723"/>
+    <mergeCell ref="E724:F724"/>
+    <mergeCell ref="E725:F725"/>
+    <mergeCell ref="E726:F726"/>
+    <mergeCell ref="E727:F727"/>
+    <mergeCell ref="E753:F753"/>
+    <mergeCell ref="E754:F754"/>
+    <mergeCell ref="E755:F755"/>
+    <mergeCell ref="E756:F756"/>
+    <mergeCell ref="E757:F757"/>
+    <mergeCell ref="E758:F758"/>
+    <mergeCell ref="E747:F747"/>
+    <mergeCell ref="E748:F748"/>
+    <mergeCell ref="E749:F749"/>
+    <mergeCell ref="E750:F750"/>
+    <mergeCell ref="E751:F751"/>
+    <mergeCell ref="E752:F752"/>
+    <mergeCell ref="E741:F741"/>
+    <mergeCell ref="E742:F742"/>
+    <mergeCell ref="E743:F743"/>
+    <mergeCell ref="E744:F744"/>
+    <mergeCell ref="E745:F745"/>
+    <mergeCell ref="E746:F746"/>
+    <mergeCell ref="E772:F772"/>
+    <mergeCell ref="E773:F773"/>
+    <mergeCell ref="E774:F774"/>
+    <mergeCell ref="E775:F775"/>
+    <mergeCell ref="E776:F776"/>
+    <mergeCell ref="E777:F777"/>
+    <mergeCell ref="E766:F766"/>
+    <mergeCell ref="E767:F767"/>
+    <mergeCell ref="E768:F768"/>
+    <mergeCell ref="E769:F769"/>
+    <mergeCell ref="E770:F770"/>
+    <mergeCell ref="E771:F771"/>
+    <mergeCell ref="E759:F759"/>
+    <mergeCell ref="E760:F760"/>
+    <mergeCell ref="E761:F761"/>
+    <mergeCell ref="E762:F762"/>
+    <mergeCell ref="E764:F764"/>
+    <mergeCell ref="E765:F765"/>
+    <mergeCell ref="E791:F791"/>
+    <mergeCell ref="E792:F792"/>
+    <mergeCell ref="E793:F793"/>
+    <mergeCell ref="E794:F794"/>
+    <mergeCell ref="E795:F795"/>
+    <mergeCell ref="E796:F796"/>
+    <mergeCell ref="E784:F784"/>
+    <mergeCell ref="E785:F785"/>
+    <mergeCell ref="E787:F787"/>
+    <mergeCell ref="E788:F788"/>
+    <mergeCell ref="E789:F789"/>
+    <mergeCell ref="E790:F790"/>
+    <mergeCell ref="E778:F778"/>
+    <mergeCell ref="E779:F779"/>
+    <mergeCell ref="E780:F780"/>
+    <mergeCell ref="E781:F781"/>
+    <mergeCell ref="E782:F782"/>
+    <mergeCell ref="E783:F783"/>
+    <mergeCell ref="E810:F810"/>
+    <mergeCell ref="E811:F811"/>
+    <mergeCell ref="E812:F812"/>
+    <mergeCell ref="E813:F813"/>
+    <mergeCell ref="E814:F814"/>
+    <mergeCell ref="E815:F815"/>
+    <mergeCell ref="E803:F803"/>
+    <mergeCell ref="E804:F804"/>
+    <mergeCell ref="E805:F805"/>
+    <mergeCell ref="E806:F806"/>
+    <mergeCell ref="E807:F807"/>
+    <mergeCell ref="E808:F808"/>
+    <mergeCell ref="E797:F797"/>
+    <mergeCell ref="E798:F798"/>
+    <mergeCell ref="E799:F799"/>
+    <mergeCell ref="E800:F800"/>
+    <mergeCell ref="E801:F801"/>
+    <mergeCell ref="E802:F802"/>
+    <mergeCell ref="E828:F828"/>
+    <mergeCell ref="E829:F829"/>
+    <mergeCell ref="E830:F830"/>
+    <mergeCell ref="E831:F831"/>
+    <mergeCell ref="E833:F833"/>
+    <mergeCell ref="E834:F834"/>
+    <mergeCell ref="E822:F822"/>
+    <mergeCell ref="E823:F823"/>
+    <mergeCell ref="E824:F824"/>
+    <mergeCell ref="E825:F825"/>
+    <mergeCell ref="E826:F826"/>
+    <mergeCell ref="E827:F827"/>
+    <mergeCell ref="E816:F816"/>
+    <mergeCell ref="E817:F817"/>
+    <mergeCell ref="E818:F818"/>
+    <mergeCell ref="E819:F819"/>
+    <mergeCell ref="E820:F820"/>
+    <mergeCell ref="E821:F821"/>
+    <mergeCell ref="E847:F847"/>
+    <mergeCell ref="E848:F848"/>
+    <mergeCell ref="E849:F849"/>
+    <mergeCell ref="E850:F850"/>
+    <mergeCell ref="E851:F851"/>
+    <mergeCell ref="E852:F852"/>
+    <mergeCell ref="E841:F841"/>
+    <mergeCell ref="E842:F842"/>
+    <mergeCell ref="E843:F843"/>
+    <mergeCell ref="E844:F844"/>
+    <mergeCell ref="E845:F845"/>
+    <mergeCell ref="E846:F846"/>
+    <mergeCell ref="E835:F835"/>
+    <mergeCell ref="E836:F836"/>
+    <mergeCell ref="E837:F837"/>
+    <mergeCell ref="E838:F838"/>
+    <mergeCell ref="E839:F839"/>
+    <mergeCell ref="E840:F840"/>
+    <mergeCell ref="E866:F866"/>
+    <mergeCell ref="E867:F867"/>
+    <mergeCell ref="E868:F868"/>
+    <mergeCell ref="E869:F869"/>
+    <mergeCell ref="E870:F870"/>
+    <mergeCell ref="E871:F871"/>
+    <mergeCell ref="E860:F860"/>
+    <mergeCell ref="E861:F861"/>
+    <mergeCell ref="E862:F862"/>
+    <mergeCell ref="E863:F863"/>
+    <mergeCell ref="E864:F864"/>
+    <mergeCell ref="E865:F865"/>
+    <mergeCell ref="E853:F853"/>
+    <mergeCell ref="E854:F854"/>
+    <mergeCell ref="E856:F856"/>
+    <mergeCell ref="E857:F857"/>
+    <mergeCell ref="E858:F858"/>
+    <mergeCell ref="E859:F859"/>
+    <mergeCell ref="E885:F885"/>
+    <mergeCell ref="E886:F886"/>
+    <mergeCell ref="E887:F887"/>
+    <mergeCell ref="E888:F888"/>
+    <mergeCell ref="E889:F889"/>
+    <mergeCell ref="E890:F890"/>
+    <mergeCell ref="E879:F879"/>
+    <mergeCell ref="E880:F880"/>
+    <mergeCell ref="E881:F881"/>
+    <mergeCell ref="E882:F882"/>
+    <mergeCell ref="E883:F883"/>
+    <mergeCell ref="E884:F884"/>
+    <mergeCell ref="E872:F872"/>
+    <mergeCell ref="E873:F873"/>
+    <mergeCell ref="E874:F874"/>
+    <mergeCell ref="E875:F875"/>
+    <mergeCell ref="E876:F876"/>
+    <mergeCell ref="E877:F877"/>
+    <mergeCell ref="E904:F904"/>
+    <mergeCell ref="E905:F905"/>
+    <mergeCell ref="E906:F906"/>
+    <mergeCell ref="E907:F907"/>
+    <mergeCell ref="E908:F908"/>
+    <mergeCell ref="E909:F909"/>
+    <mergeCell ref="E897:F897"/>
+    <mergeCell ref="E898:F898"/>
+    <mergeCell ref="E899:F899"/>
+    <mergeCell ref="E900:F900"/>
+    <mergeCell ref="E902:F902"/>
+    <mergeCell ref="E903:F903"/>
+    <mergeCell ref="E891:F891"/>
+    <mergeCell ref="E892:F892"/>
+    <mergeCell ref="E893:F893"/>
+    <mergeCell ref="E894:F894"/>
+    <mergeCell ref="E895:F895"/>
+    <mergeCell ref="E896:F896"/>
+    <mergeCell ref="E922:F922"/>
+    <mergeCell ref="E923:F923"/>
+    <mergeCell ref="E925:F925"/>
+    <mergeCell ref="E926:F926"/>
+    <mergeCell ref="E927:F927"/>
+    <mergeCell ref="E928:F928"/>
+    <mergeCell ref="E916:F916"/>
+    <mergeCell ref="E917:F917"/>
+    <mergeCell ref="E918:F918"/>
+    <mergeCell ref="E919:F919"/>
+    <mergeCell ref="E920:F920"/>
+    <mergeCell ref="E921:F921"/>
+    <mergeCell ref="E910:F910"/>
+    <mergeCell ref="E911:F911"/>
+    <mergeCell ref="E912:F912"/>
+    <mergeCell ref="E913:F913"/>
+    <mergeCell ref="E914:F914"/>
+    <mergeCell ref="E915:F915"/>
+    <mergeCell ref="E941:F941"/>
+    <mergeCell ref="E942:F942"/>
+    <mergeCell ref="E943:F943"/>
+    <mergeCell ref="E944:F944"/>
+    <mergeCell ref="E945:F945"/>
+    <mergeCell ref="E946:F946"/>
+    <mergeCell ref="E935:F935"/>
+    <mergeCell ref="E936:F936"/>
+    <mergeCell ref="E937:F937"/>
+    <mergeCell ref="E938:F938"/>
+    <mergeCell ref="E939:F939"/>
+    <mergeCell ref="E940:F940"/>
+    <mergeCell ref="E929:F929"/>
+    <mergeCell ref="E930:F930"/>
+    <mergeCell ref="E931:F931"/>
+    <mergeCell ref="E932:F932"/>
+    <mergeCell ref="E933:F933"/>
+    <mergeCell ref="E934:F934"/>
+    <mergeCell ref="E966:F966"/>
+    <mergeCell ref="E967:F967"/>
+    <mergeCell ref="E968:F968"/>
+    <mergeCell ref="E969:F969"/>
+    <mergeCell ref="E960:F960"/>
+    <mergeCell ref="E961:F961"/>
+    <mergeCell ref="E962:F962"/>
+    <mergeCell ref="E963:F963"/>
+    <mergeCell ref="E964:F964"/>
+    <mergeCell ref="E965:F965"/>
+    <mergeCell ref="E954:F954"/>
+    <mergeCell ref="E955:F955"/>
+    <mergeCell ref="E956:F956"/>
+    <mergeCell ref="E957:F957"/>
+    <mergeCell ref="E958:F958"/>
+    <mergeCell ref="E959:F959"/>
+    <mergeCell ref="E948:F948"/>
+    <mergeCell ref="E949:F949"/>
+    <mergeCell ref="E950:F950"/>
+    <mergeCell ref="E951:F951"/>
+    <mergeCell ref="E952:F952"/>
+    <mergeCell ref="E953:F953"/>
+    <mergeCell ref="E985:F985"/>
+    <mergeCell ref="E986:F986"/>
+    <mergeCell ref="E987:F987"/>
+    <mergeCell ref="E988:F988"/>
+    <mergeCell ref="E989:F989"/>
+    <mergeCell ref="E990:F990"/>
+    <mergeCell ref="E979:F979"/>
+    <mergeCell ref="E980:F980"/>
+    <mergeCell ref="E981:F981"/>
+    <mergeCell ref="E982:F982"/>
+    <mergeCell ref="E983:F983"/>
+    <mergeCell ref="E984:F984"/>
+    <mergeCell ref="E971:F971"/>
+    <mergeCell ref="E972:F972"/>
+    <mergeCell ref="E973:F973"/>
+    <mergeCell ref="E974:F974"/>
+    <mergeCell ref="E975:F975"/>
+    <mergeCell ref="E976:F976"/>
+    <mergeCell ref="E977:F977"/>
+    <mergeCell ref="E978:F978"/>
+    <mergeCell ref="E1004:F1004"/>
+    <mergeCell ref="E1005:F1005"/>
+    <mergeCell ref="E1006:F1006"/>
+    <mergeCell ref="E1007:F1007"/>
+    <mergeCell ref="E1008:F1008"/>
+    <mergeCell ref="E1009:F1009"/>
+    <mergeCell ref="E998:F998"/>
+    <mergeCell ref="E999:F999"/>
+    <mergeCell ref="E1000:F1000"/>
+    <mergeCell ref="E1001:F1001"/>
+    <mergeCell ref="E1002:F1002"/>
+    <mergeCell ref="E1003:F1003"/>
+    <mergeCell ref="E991:F991"/>
+    <mergeCell ref="E992:F992"/>
+    <mergeCell ref="E994:F994"/>
+    <mergeCell ref="E995:F995"/>
+    <mergeCell ref="E996:F996"/>
+    <mergeCell ref="E997:F997"/>
+    <mergeCell ref="E1023:F1023"/>
+    <mergeCell ref="E1024:F1024"/>
+    <mergeCell ref="E1025:F1025"/>
+    <mergeCell ref="E1026:F1026"/>
+    <mergeCell ref="E1027:F1027"/>
+    <mergeCell ref="E1028:F1028"/>
+    <mergeCell ref="E1017:F1017"/>
+    <mergeCell ref="E1018:F1018"/>
+    <mergeCell ref="E1019:F1019"/>
+    <mergeCell ref="E1020:F1020"/>
+    <mergeCell ref="E1021:F1021"/>
+    <mergeCell ref="E1022:F1022"/>
+    <mergeCell ref="E1010:F1010"/>
+    <mergeCell ref="E1011:F1011"/>
+    <mergeCell ref="E1012:F1012"/>
+    <mergeCell ref="E1013:F1013"/>
+    <mergeCell ref="E1014:F1014"/>
+    <mergeCell ref="E1015:F1015"/>
+    <mergeCell ref="E1042:F1042"/>
+    <mergeCell ref="E1043:F1043"/>
+    <mergeCell ref="E1044:F1044"/>
+    <mergeCell ref="E1045:F1045"/>
+    <mergeCell ref="E1046:F1046"/>
+    <mergeCell ref="E1047:F1047"/>
+    <mergeCell ref="E1035:F1035"/>
+    <mergeCell ref="E1036:F1036"/>
+    <mergeCell ref="E1037:F1037"/>
+    <mergeCell ref="E1038:F1038"/>
+    <mergeCell ref="E1040:F1040"/>
+    <mergeCell ref="E1041:F1041"/>
+    <mergeCell ref="E1029:F1029"/>
+    <mergeCell ref="E1030:F1030"/>
+    <mergeCell ref="E1031:F1031"/>
+    <mergeCell ref="E1032:F1032"/>
+    <mergeCell ref="E1033:F1033"/>
+    <mergeCell ref="E1034:F1034"/>
+    <mergeCell ref="E1060:F1060"/>
+    <mergeCell ref="E1061:F1061"/>
+    <mergeCell ref="E1063:F1063"/>
+    <mergeCell ref="E1064:F1064"/>
+    <mergeCell ref="E1065:F1065"/>
+    <mergeCell ref="E1066:F1066"/>
+    <mergeCell ref="E1054:F1054"/>
+    <mergeCell ref="E1055:F1055"/>
+    <mergeCell ref="E1056:F1056"/>
+    <mergeCell ref="E1057:F1057"/>
+    <mergeCell ref="E1058:F1058"/>
+    <mergeCell ref="E1059:F1059"/>
+    <mergeCell ref="E1048:F1048"/>
+    <mergeCell ref="E1049:F1049"/>
+    <mergeCell ref="E1050:F1050"/>
+    <mergeCell ref="E1051:F1051"/>
+    <mergeCell ref="E1052:F1052"/>
+    <mergeCell ref="E1053:F1053"/>
+    <mergeCell ref="E1079:F1079"/>
+    <mergeCell ref="E1080:F1080"/>
+    <mergeCell ref="E1081:F1081"/>
+    <mergeCell ref="E1082:F1082"/>
+    <mergeCell ref="E1083:F1083"/>
+    <mergeCell ref="E1084:F1084"/>
+    <mergeCell ref="E1073:F1073"/>
+    <mergeCell ref="E1074:F1074"/>
+    <mergeCell ref="E1075:F1075"/>
+    <mergeCell ref="E1076:F1076"/>
+    <mergeCell ref="E1077:F1077"/>
+    <mergeCell ref="E1078:F1078"/>
+    <mergeCell ref="E1067:F1067"/>
+    <mergeCell ref="E1068:F1068"/>
+    <mergeCell ref="E1069:F1069"/>
+    <mergeCell ref="E1070:F1070"/>
+    <mergeCell ref="E1071:F1071"/>
+    <mergeCell ref="E1072:F1072"/>
+    <mergeCell ref="E1098:F1098"/>
+    <mergeCell ref="E1099:F1099"/>
+    <mergeCell ref="E1100:F1100"/>
+    <mergeCell ref="E1101:F1101"/>
+    <mergeCell ref="E1102:F1102"/>
+    <mergeCell ref="E1103:F1103"/>
+    <mergeCell ref="E1092:F1092"/>
+    <mergeCell ref="E1093:F1093"/>
+    <mergeCell ref="E1094:F1094"/>
+    <mergeCell ref="E1095:F1095"/>
+    <mergeCell ref="E1096:F1096"/>
+    <mergeCell ref="E1097:F1097"/>
+    <mergeCell ref="E1086:F1086"/>
+    <mergeCell ref="E1087:F1087"/>
+    <mergeCell ref="E1088:F1088"/>
+    <mergeCell ref="E1089:F1089"/>
+    <mergeCell ref="E1090:F1090"/>
+    <mergeCell ref="E1091:F1091"/>
+    <mergeCell ref="E1117:F1117"/>
+    <mergeCell ref="E1118:F1118"/>
+    <mergeCell ref="E1119:F1119"/>
+    <mergeCell ref="E1120:F1120"/>
+    <mergeCell ref="E1121:F1121"/>
+    <mergeCell ref="E1122:F1122"/>
+    <mergeCell ref="E1111:F1111"/>
+    <mergeCell ref="E1112:F1112"/>
+    <mergeCell ref="E1113:F1113"/>
+    <mergeCell ref="E1114:F1114"/>
+    <mergeCell ref="E1115:F1115"/>
+    <mergeCell ref="E1116:F1116"/>
+    <mergeCell ref="E1104:F1104"/>
+    <mergeCell ref="E1105:F1105"/>
+    <mergeCell ref="E1106:F1106"/>
+    <mergeCell ref="E1107:F1107"/>
+    <mergeCell ref="E1109:F1109"/>
+    <mergeCell ref="E1110:F1110"/>
+    <mergeCell ref="E1136:F1136"/>
+    <mergeCell ref="E1137:F1137"/>
+    <mergeCell ref="E1138:F1138"/>
+    <mergeCell ref="E1139:F1139"/>
+    <mergeCell ref="E1140:F1140"/>
+    <mergeCell ref="E1141:F1141"/>
+    <mergeCell ref="E1129:F1129"/>
+    <mergeCell ref="E1130:F1130"/>
+    <mergeCell ref="E1132:F1132"/>
+    <mergeCell ref="E1133:F1133"/>
+    <mergeCell ref="E1134:F1134"/>
+    <mergeCell ref="E1135:F1135"/>
+    <mergeCell ref="E1123:F1123"/>
+    <mergeCell ref="E1124:F1124"/>
+    <mergeCell ref="E1125:F1125"/>
+    <mergeCell ref="E1126:F1126"/>
+    <mergeCell ref="E1127:F1127"/>
+    <mergeCell ref="E1128:F1128"/>
+    <mergeCell ref="E1155:F1155"/>
+    <mergeCell ref="E1156:F1156"/>
+    <mergeCell ref="E1157:F1157"/>
+    <mergeCell ref="E1158:F1158"/>
+    <mergeCell ref="E1159:F1159"/>
+    <mergeCell ref="E1160:F1160"/>
+    <mergeCell ref="E1148:F1148"/>
+    <mergeCell ref="E1149:F1149"/>
+    <mergeCell ref="E1150:F1150"/>
+    <mergeCell ref="E1151:F1151"/>
+    <mergeCell ref="E1152:F1152"/>
+    <mergeCell ref="E1153:F1153"/>
+    <mergeCell ref="E1142:F1142"/>
+    <mergeCell ref="E1143:F1143"/>
+    <mergeCell ref="E1144:F1144"/>
+    <mergeCell ref="E1145:F1145"/>
+    <mergeCell ref="E1146:F1146"/>
+    <mergeCell ref="E1147:F1147"/>
+    <mergeCell ref="E1173:F1173"/>
+    <mergeCell ref="E1174:F1174"/>
+    <mergeCell ref="E1175:F1175"/>
+    <mergeCell ref="E1176:F1176"/>
+    <mergeCell ref="E1178:F1178"/>
+    <mergeCell ref="E1179:F1179"/>
+    <mergeCell ref="E1167:F1167"/>
+    <mergeCell ref="E1168:F1168"/>
+    <mergeCell ref="E1169:F1169"/>
+    <mergeCell ref="E1170:F1170"/>
+    <mergeCell ref="E1171:F1171"/>
+    <mergeCell ref="E1172:F1172"/>
+    <mergeCell ref="E1161:F1161"/>
+    <mergeCell ref="E1162:F1162"/>
+    <mergeCell ref="E1163:F1163"/>
+    <mergeCell ref="E1164:F1164"/>
+    <mergeCell ref="E1165:F1165"/>
+    <mergeCell ref="E1166:F1166"/>
+    <mergeCell ref="E1192:F1192"/>
+    <mergeCell ref="E1193:F1193"/>
+    <mergeCell ref="E1194:F1194"/>
+    <mergeCell ref="E1195:F1195"/>
+    <mergeCell ref="E1196:F1196"/>
+    <mergeCell ref="E1197:F1197"/>
+    <mergeCell ref="E1186:F1186"/>
+    <mergeCell ref="E1187:F1187"/>
+    <mergeCell ref="E1188:F1188"/>
+    <mergeCell ref="E1189:F1189"/>
+    <mergeCell ref="E1190:F1190"/>
+    <mergeCell ref="E1191:F1191"/>
+    <mergeCell ref="E1180:F1180"/>
+    <mergeCell ref="E1181:F1181"/>
+    <mergeCell ref="E1182:F1182"/>
+    <mergeCell ref="E1183:F1183"/>
+    <mergeCell ref="E1184:F1184"/>
+    <mergeCell ref="E1185:F1185"/>
+    <mergeCell ref="E1211:F1211"/>
+    <mergeCell ref="E1212:F1212"/>
+    <mergeCell ref="E1213:F1213"/>
+    <mergeCell ref="E1214:F1214"/>
+    <mergeCell ref="E1215:F1215"/>
+    <mergeCell ref="E1216:F1216"/>
+    <mergeCell ref="E1205:F1205"/>
+    <mergeCell ref="E1206:F1206"/>
+    <mergeCell ref="E1207:F1207"/>
+    <mergeCell ref="E1208:F1208"/>
+    <mergeCell ref="E1209:F1209"/>
+    <mergeCell ref="E1210:F1210"/>
+    <mergeCell ref="E1198:F1198"/>
+    <mergeCell ref="E1199:F1199"/>
+    <mergeCell ref="E1201:F1201"/>
+    <mergeCell ref="E1202:F1202"/>
+    <mergeCell ref="E1203:F1203"/>
+    <mergeCell ref="E1204:F1204"/>
+    <mergeCell ref="E1230:F1230"/>
+    <mergeCell ref="E1231:F1231"/>
+    <mergeCell ref="E1232:F1232"/>
+    <mergeCell ref="E1233:F1233"/>
+    <mergeCell ref="E1234:F1234"/>
+    <mergeCell ref="E1235:F1235"/>
+    <mergeCell ref="E1224:F1224"/>
+    <mergeCell ref="E1225:F1225"/>
+    <mergeCell ref="E1226:F1226"/>
+    <mergeCell ref="E1227:F1227"/>
+    <mergeCell ref="E1228:F1228"/>
+    <mergeCell ref="E1229:F1229"/>
+    <mergeCell ref="E1217:F1217"/>
+    <mergeCell ref="E1218:F1218"/>
+    <mergeCell ref="E1219:F1219"/>
+    <mergeCell ref="E1220:F1220"/>
+    <mergeCell ref="E1221:F1221"/>
+    <mergeCell ref="E1222:F1222"/>
+    <mergeCell ref="E1249:F1249"/>
+    <mergeCell ref="E1250:F1250"/>
+    <mergeCell ref="E1251:F1251"/>
+    <mergeCell ref="E1252:F1252"/>
+    <mergeCell ref="E1253:F1253"/>
+    <mergeCell ref="E1254:F1254"/>
+    <mergeCell ref="E1242:F1242"/>
+    <mergeCell ref="E1243:F1243"/>
+    <mergeCell ref="E1244:F1244"/>
+    <mergeCell ref="E1245:F1245"/>
+    <mergeCell ref="E1247:F1247"/>
+    <mergeCell ref="E1248:F1248"/>
+    <mergeCell ref="E1236:F1236"/>
+    <mergeCell ref="E1237:F1237"/>
+    <mergeCell ref="E1238:F1238"/>
+    <mergeCell ref="E1239:F1239"/>
+    <mergeCell ref="E1240:F1240"/>
+    <mergeCell ref="E1241:F1241"/>
+    <mergeCell ref="E1267:F1267"/>
+    <mergeCell ref="E1268:F1268"/>
+    <mergeCell ref="E1270:F1270"/>
+    <mergeCell ref="E1271:F1271"/>
+    <mergeCell ref="E1272:F1272"/>
+    <mergeCell ref="E1273:F1273"/>
+    <mergeCell ref="E1261:F1261"/>
+    <mergeCell ref="E1262:F1262"/>
+    <mergeCell ref="E1263:F1263"/>
+    <mergeCell ref="E1264:F1264"/>
+    <mergeCell ref="E1265:F1265"/>
+    <mergeCell ref="E1266:F1266"/>
+    <mergeCell ref="E1255:F1255"/>
+    <mergeCell ref="E1256:F1256"/>
+    <mergeCell ref="E1257:F1257"/>
+    <mergeCell ref="E1258:F1258"/>
+    <mergeCell ref="E1259:F1259"/>
+    <mergeCell ref="E1260:F1260"/>
+    <mergeCell ref="E1286:F1286"/>
+    <mergeCell ref="E1287:F1287"/>
+    <mergeCell ref="E1288:F1288"/>
+    <mergeCell ref="E1289:F1289"/>
+    <mergeCell ref="E1290:F1290"/>
+    <mergeCell ref="E1291:F1291"/>
+    <mergeCell ref="E1280:F1280"/>
+    <mergeCell ref="E1281:F1281"/>
+    <mergeCell ref="E1282:F1282"/>
+    <mergeCell ref="E1283:F1283"/>
+    <mergeCell ref="E1284:F1284"/>
+    <mergeCell ref="E1285:F1285"/>
+    <mergeCell ref="E1274:F1274"/>
+    <mergeCell ref="E1275:F1275"/>
+    <mergeCell ref="E1276:F1276"/>
+    <mergeCell ref="E1277:F1277"/>
+    <mergeCell ref="E1278:F1278"/>
+    <mergeCell ref="E1279:F1279"/>
+    <mergeCell ref="E1305:F1305"/>
+    <mergeCell ref="E1306:F1306"/>
+    <mergeCell ref="E1307:F1307"/>
+    <mergeCell ref="E1308:F1308"/>
+    <mergeCell ref="E1309:F1309"/>
+    <mergeCell ref="E1310:F1310"/>
+    <mergeCell ref="E1299:F1299"/>
+    <mergeCell ref="E1300:F1300"/>
+    <mergeCell ref="E1301:F1301"/>
+    <mergeCell ref="E1302:F1302"/>
+    <mergeCell ref="E1303:F1303"/>
+    <mergeCell ref="E1304:F1304"/>
+    <mergeCell ref="E1293:F1293"/>
+    <mergeCell ref="E1294:F1294"/>
+    <mergeCell ref="E1295:F1295"/>
+    <mergeCell ref="E1296:F1296"/>
+    <mergeCell ref="E1297:F1297"/>
+    <mergeCell ref="E1298:F1298"/>
+    <mergeCell ref="E1324:F1324"/>
+    <mergeCell ref="E1325:F1325"/>
+    <mergeCell ref="E1326:F1326"/>
+    <mergeCell ref="E1327:F1327"/>
+    <mergeCell ref="E1328:F1328"/>
+    <mergeCell ref="E1329:F1329"/>
+    <mergeCell ref="E1318:F1318"/>
+    <mergeCell ref="E1319:F1319"/>
+    <mergeCell ref="E1320:F1320"/>
+    <mergeCell ref="E1321:F1321"/>
+    <mergeCell ref="E1322:F1322"/>
+    <mergeCell ref="E1323:F1323"/>
+    <mergeCell ref="E1311:F1311"/>
+    <mergeCell ref="E1312:F1312"/>
+    <mergeCell ref="E1313:F1313"/>
+    <mergeCell ref="E1314:F1314"/>
+    <mergeCell ref="E1316:F1316"/>
+    <mergeCell ref="E1317:F1317"/>
+    <mergeCell ref="E1343:F1343"/>
+    <mergeCell ref="E1344:F1344"/>
+    <mergeCell ref="E1345:F1345"/>
+    <mergeCell ref="E1346:F1346"/>
+    <mergeCell ref="E1347:F1347"/>
+    <mergeCell ref="E1348:F1348"/>
+    <mergeCell ref="E1336:F1336"/>
+    <mergeCell ref="E1337:F1337"/>
+    <mergeCell ref="E1339:F1339"/>
+    <mergeCell ref="E1340:F1340"/>
+    <mergeCell ref="E1341:F1341"/>
+    <mergeCell ref="E1342:F1342"/>
+    <mergeCell ref="E1330:F1330"/>
+    <mergeCell ref="E1331:F1331"/>
+    <mergeCell ref="E1332:F1332"/>
+    <mergeCell ref="E1333:F1333"/>
+    <mergeCell ref="E1334:F1334"/>
+    <mergeCell ref="E1335:F1335"/>
+    <mergeCell ref="E1362:F1362"/>
+    <mergeCell ref="E1363:F1363"/>
+    <mergeCell ref="E1364:F1364"/>
+    <mergeCell ref="E1365:F1365"/>
+    <mergeCell ref="E1366:F1366"/>
+    <mergeCell ref="E1367:F1367"/>
+    <mergeCell ref="E1355:F1355"/>
+    <mergeCell ref="E1356:F1356"/>
+    <mergeCell ref="E1357:F1357"/>
+    <mergeCell ref="E1358:F1358"/>
+    <mergeCell ref="E1359:F1359"/>
+    <mergeCell ref="E1360:F1360"/>
+    <mergeCell ref="E1349:F1349"/>
+    <mergeCell ref="E1350:F1350"/>
+    <mergeCell ref="E1351:F1351"/>
+    <mergeCell ref="E1352:F1352"/>
+    <mergeCell ref="E1353:F1353"/>
+    <mergeCell ref="E1354:F1354"/>
+    <mergeCell ref="E1380:F1380"/>
+    <mergeCell ref="E1381:F1381"/>
+    <mergeCell ref="E1382:F1382"/>
+    <mergeCell ref="E1383:F1383"/>
+    <mergeCell ref="E1385:F1385"/>
+    <mergeCell ref="E1386:F1386"/>
+    <mergeCell ref="E1374:F1374"/>
+    <mergeCell ref="E1375:F1375"/>
+    <mergeCell ref="E1376:F1376"/>
+    <mergeCell ref="E1377:F1377"/>
+    <mergeCell ref="E1378:F1378"/>
+    <mergeCell ref="E1379:F1379"/>
+    <mergeCell ref="E1368:F1368"/>
+    <mergeCell ref="E1369:F1369"/>
+    <mergeCell ref="E1370:F1370"/>
+    <mergeCell ref="E1371:F1371"/>
+    <mergeCell ref="E1372:F1372"/>
+    <mergeCell ref="E1373:F1373"/>
+    <mergeCell ref="E1399:F1399"/>
+    <mergeCell ref="E1400:F1400"/>
+    <mergeCell ref="E1401:F1401"/>
+    <mergeCell ref="E1402:F1402"/>
+    <mergeCell ref="E1403:F1403"/>
+    <mergeCell ref="E1404:F1404"/>
+    <mergeCell ref="E1393:F1393"/>
+    <mergeCell ref="E1394:F1394"/>
+    <mergeCell ref="E1395:F1395"/>
+    <mergeCell ref="E1396:F1396"/>
+    <mergeCell ref="E1397:F1397"/>
+    <mergeCell ref="E1398:F1398"/>
+    <mergeCell ref="E1387:F1387"/>
+    <mergeCell ref="E1388:F1388"/>
+    <mergeCell ref="E1389:F1389"/>
+    <mergeCell ref="E1390:F1390"/>
+    <mergeCell ref="E1391:F1391"/>
+    <mergeCell ref="E1392:F1392"/>
+    <mergeCell ref="E1418:F1418"/>
+    <mergeCell ref="E1419:F1419"/>
+    <mergeCell ref="E1420:F1420"/>
+    <mergeCell ref="E1421:F1421"/>
+    <mergeCell ref="E1422:F1422"/>
+    <mergeCell ref="E1423:F1423"/>
+    <mergeCell ref="E1412:F1412"/>
+    <mergeCell ref="E1413:F1413"/>
+    <mergeCell ref="E1414:F1414"/>
+    <mergeCell ref="E1415:F1415"/>
+    <mergeCell ref="E1416:F1416"/>
+    <mergeCell ref="E1417:F1417"/>
+    <mergeCell ref="E1405:F1405"/>
+    <mergeCell ref="E1406:F1406"/>
+    <mergeCell ref="E1408:F1408"/>
+    <mergeCell ref="E1409:F1409"/>
+    <mergeCell ref="E1410:F1410"/>
+    <mergeCell ref="E1411:F1411"/>
+    <mergeCell ref="E1437:F1437"/>
+    <mergeCell ref="E1438:F1438"/>
+    <mergeCell ref="E1439:F1439"/>
+    <mergeCell ref="E1440:F1440"/>
+    <mergeCell ref="E1441:F1441"/>
+    <mergeCell ref="E1442:F1442"/>
+    <mergeCell ref="E1431:F1431"/>
+    <mergeCell ref="E1432:F1432"/>
+    <mergeCell ref="E1433:F1433"/>
+    <mergeCell ref="E1434:F1434"/>
+    <mergeCell ref="E1435:F1435"/>
+    <mergeCell ref="E1436:F1436"/>
+    <mergeCell ref="E1424:F1424"/>
+    <mergeCell ref="E1425:F1425"/>
+    <mergeCell ref="E1426:F1426"/>
+    <mergeCell ref="E1427:F1427"/>
+    <mergeCell ref="E1428:F1428"/>
+    <mergeCell ref="E1429:F1429"/>
+    <mergeCell ref="E1456:F1456"/>
+    <mergeCell ref="E1457:F1457"/>
+    <mergeCell ref="E1458:F1458"/>
+    <mergeCell ref="E1459:F1459"/>
+    <mergeCell ref="E1460:F1460"/>
+    <mergeCell ref="E1461:F1461"/>
+    <mergeCell ref="E1449:F1449"/>
+    <mergeCell ref="E1450:F1450"/>
+    <mergeCell ref="E1451:F1451"/>
+    <mergeCell ref="E1452:F1452"/>
+    <mergeCell ref="E1454:F1454"/>
+    <mergeCell ref="E1455:F1455"/>
+    <mergeCell ref="E1443:F1443"/>
+    <mergeCell ref="E1444:F1444"/>
+    <mergeCell ref="E1445:F1445"/>
+    <mergeCell ref="E1446:F1446"/>
+    <mergeCell ref="E1447:F1447"/>
+    <mergeCell ref="E1448:F1448"/>
+    <mergeCell ref="E1474:F1474"/>
+    <mergeCell ref="E1475:F1475"/>
+    <mergeCell ref="E1477:F1477"/>
+    <mergeCell ref="E1478:F1478"/>
+    <mergeCell ref="E1479:F1479"/>
+    <mergeCell ref="E1480:F1480"/>
+    <mergeCell ref="E1468:F1468"/>
+    <mergeCell ref="E1469:F1469"/>
+    <mergeCell ref="E1470:F1470"/>
+    <mergeCell ref="E1471:F1471"/>
+    <mergeCell ref="E1472:F1472"/>
+    <mergeCell ref="E1473:F1473"/>
+    <mergeCell ref="E1462:F1462"/>
+    <mergeCell ref="E1463:F1463"/>
+    <mergeCell ref="E1464:F1464"/>
+    <mergeCell ref="E1465:F1465"/>
+    <mergeCell ref="E1466:F1466"/>
+    <mergeCell ref="E1467:F1467"/>
+    <mergeCell ref="E1505:F1505"/>
+    <mergeCell ref="E1493:F1493"/>
+    <mergeCell ref="E1494:F1494"/>
+    <mergeCell ref="E1495:F1495"/>
+    <mergeCell ref="E1496:F1496"/>
+    <mergeCell ref="E1497:F1497"/>
+    <mergeCell ref="E1498:F1498"/>
+    <mergeCell ref="E1487:F1487"/>
+    <mergeCell ref="E1488:F1488"/>
+    <mergeCell ref="E1489:F1489"/>
+    <mergeCell ref="E1490:F1490"/>
+    <mergeCell ref="E1491:F1491"/>
+    <mergeCell ref="E1492:F1492"/>
+    <mergeCell ref="E1481:F1481"/>
+    <mergeCell ref="E1482:F1482"/>
+    <mergeCell ref="E1483:F1483"/>
+    <mergeCell ref="E1484:F1484"/>
+    <mergeCell ref="E1485:F1485"/>
+    <mergeCell ref="E1486:F1486"/>
+    <mergeCell ref="E416:F416"/>
+    <mergeCell ref="E414:F414"/>
+    <mergeCell ref="E412:F412"/>
+    <mergeCell ref="E410:F410"/>
+    <mergeCell ref="E408:F408"/>
+    <mergeCell ref="E406:F406"/>
+    <mergeCell ref="E404:F404"/>
+    <mergeCell ref="E402:F402"/>
+    <mergeCell ref="E400:F400"/>
+    <mergeCell ref="E398:F398"/>
+    <mergeCell ref="E396:F396"/>
+    <mergeCell ref="E1518:F1518"/>
+    <mergeCell ref="E1519:F1519"/>
+    <mergeCell ref="E1520:F1520"/>
+    <mergeCell ref="E1521:F1521"/>
+    <mergeCell ref="E1512:F1512"/>
+    <mergeCell ref="E1513:F1513"/>
+    <mergeCell ref="E1514:F1514"/>
+    <mergeCell ref="E1515:F1515"/>
+    <mergeCell ref="E1516:F1516"/>
+    <mergeCell ref="E1517:F1517"/>
+    <mergeCell ref="E1506:F1506"/>
+    <mergeCell ref="E1507:F1507"/>
+    <mergeCell ref="E1508:F1508"/>
+    <mergeCell ref="E1509:F1509"/>
+    <mergeCell ref="E1510:F1510"/>
+    <mergeCell ref="E1511:F1511"/>
+    <mergeCell ref="E1500:F1500"/>
+    <mergeCell ref="E1501:F1501"/>
+    <mergeCell ref="E1502:F1502"/>
+    <mergeCell ref="E1503:F1503"/>
+    <mergeCell ref="E1504:F1504"/>
+    <mergeCell ref="E392:F392"/>
+    <mergeCell ref="E393:F393"/>
+    <mergeCell ref="E394:F394"/>
+    <mergeCell ref="E350:F350"/>
+    <mergeCell ref="E351:F351"/>
+    <mergeCell ref="E352:F352"/>
+    <mergeCell ref="E353:F353"/>
+    <mergeCell ref="E354:F354"/>
+    <mergeCell ref="E355:F355"/>
+    <mergeCell ref="E356:F356"/>
+    <mergeCell ref="E357:F357"/>
+    <mergeCell ref="E358:F358"/>
+    <mergeCell ref="E359:F359"/>
+    <mergeCell ref="E360:F360"/>
+    <mergeCell ref="E361:F361"/>
+    <mergeCell ref="E373:F373"/>
+    <mergeCell ref="E374:F374"/>
+    <mergeCell ref="E375:F375"/>
+    <mergeCell ref="E376:F376"/>
+    <mergeCell ref="E377:F377"/>
+    <mergeCell ref="E378:F378"/>
+    <mergeCell ref="E379:F379"/>
+    <mergeCell ref="E380:F380"/>
+    <mergeCell ref="E381:F381"/>
+    <mergeCell ref="E382:F382"/>
+    <mergeCell ref="E383:F383"/>
+    <mergeCell ref="E384:F384"/>
+    <mergeCell ref="E385:F385"/>
+    <mergeCell ref="E386:F386"/>
+    <mergeCell ref="E387:F387"/>
+    <mergeCell ref="E388:F388"/>
+    <mergeCell ref="E389:F389"/>
+    <mergeCell ref="E364:F364"/>
+    <mergeCell ref="E365:F365"/>
+    <mergeCell ref="E366:F366"/>
+    <mergeCell ref="E367:F367"/>
+    <mergeCell ref="E368:F368"/>
+    <mergeCell ref="E369:F369"/>
+    <mergeCell ref="E370:F370"/>
+    <mergeCell ref="E371:F371"/>
+    <mergeCell ref="E327:F327"/>
+    <mergeCell ref="E328:F328"/>
+    <mergeCell ref="E329:F329"/>
+    <mergeCell ref="E330:F330"/>
+    <mergeCell ref="E331:F331"/>
+    <mergeCell ref="E332:F332"/>
+    <mergeCell ref="E333:F333"/>
+    <mergeCell ref="E390:F390"/>
+    <mergeCell ref="E391:F391"/>
+    <mergeCell ref="E334:F334"/>
+    <mergeCell ref="E335:F335"/>
+    <mergeCell ref="E336:F336"/>
+    <mergeCell ref="E337:F337"/>
+    <mergeCell ref="E338:F338"/>
+    <mergeCell ref="E339:F339"/>
+    <mergeCell ref="E340:F340"/>
+    <mergeCell ref="E341:F341"/>
+    <mergeCell ref="E342:F342"/>
+    <mergeCell ref="E343:F343"/>
+    <mergeCell ref="E344:F344"/>
+    <mergeCell ref="E345:F345"/>
+    <mergeCell ref="E346:F346"/>
+    <mergeCell ref="E347:F347"/>
+    <mergeCell ref="E348:F348"/>
+    <mergeCell ref="E362:F362"/>
+    <mergeCell ref="E363:F363"/>
+    <mergeCell ref="E304:F304"/>
+    <mergeCell ref="E305:F305"/>
+    <mergeCell ref="E306:F306"/>
+    <mergeCell ref="E307:F307"/>
+    <mergeCell ref="E308:F308"/>
+    <mergeCell ref="E309:F309"/>
+    <mergeCell ref="E310:F310"/>
+    <mergeCell ref="E311:F311"/>
+    <mergeCell ref="E312:F312"/>
+    <mergeCell ref="E313:F313"/>
+    <mergeCell ref="E314:F314"/>
+    <mergeCell ref="E315:F315"/>
+    <mergeCell ref="E316:F316"/>
+    <mergeCell ref="E317:F317"/>
+    <mergeCell ref="E318:F318"/>
+    <mergeCell ref="E319:F319"/>
+    <mergeCell ref="E320:F320"/>
+    <mergeCell ref="E321:F321"/>
+    <mergeCell ref="E322:F322"/>
+    <mergeCell ref="E323:F323"/>
+    <mergeCell ref="E324:F324"/>
+    <mergeCell ref="E325:F325"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="E236:F236"/>
+    <mergeCell ref="E237:F237"/>
+    <mergeCell ref="E238:F238"/>
+    <mergeCell ref="E239:F239"/>
+    <mergeCell ref="E240:F240"/>
+    <mergeCell ref="E241:F241"/>
+    <mergeCell ref="E242:F242"/>
+    <mergeCell ref="E243:F243"/>
+    <mergeCell ref="E244:F244"/>
+    <mergeCell ref="E245:F245"/>
+    <mergeCell ref="E246:F246"/>
+    <mergeCell ref="E247:F247"/>
+    <mergeCell ref="E248:F248"/>
+    <mergeCell ref="E249:F249"/>
+    <mergeCell ref="E250:F250"/>
+    <mergeCell ref="E251:F251"/>
+    <mergeCell ref="E266:F266"/>
+    <mergeCell ref="E267:F267"/>
+    <mergeCell ref="E268:F268"/>
+    <mergeCell ref="E269:F269"/>
+    <mergeCell ref="E270:F270"/>
+    <mergeCell ref="E271:F271"/>
+    <mergeCell ref="E272:F272"/>
+    <mergeCell ref="E273:F273"/>
+    <mergeCell ref="E274:F274"/>
+    <mergeCell ref="E275:F275"/>
+    <mergeCell ref="E276:F276"/>
+    <mergeCell ref="E277:F277"/>
+    <mergeCell ref="E252:F252"/>
+    <mergeCell ref="E253:F253"/>
+    <mergeCell ref="E254:F254"/>
+    <mergeCell ref="E255:F255"/>
+    <mergeCell ref="E256:F256"/>
     <mergeCell ref="E221:F221"/>
     <mergeCell ref="E222:F222"/>
     <mergeCell ref="E223:F223"/>
@@ -41842,1273 +42961,138 @@
     <mergeCell ref="E262:F262"/>
     <mergeCell ref="E263:F263"/>
     <mergeCell ref="E264:F264"/>
-    <mergeCell ref="E266:F266"/>
-    <mergeCell ref="E267:F267"/>
-    <mergeCell ref="E268:F268"/>
-    <mergeCell ref="E269:F269"/>
-    <mergeCell ref="E270:F270"/>
-    <mergeCell ref="E271:F271"/>
-    <mergeCell ref="E272:F272"/>
-    <mergeCell ref="E273:F273"/>
-    <mergeCell ref="E274:F274"/>
-    <mergeCell ref="E275:F275"/>
-    <mergeCell ref="E276:F276"/>
-    <mergeCell ref="E277:F277"/>
-    <mergeCell ref="E252:F252"/>
-    <mergeCell ref="E253:F253"/>
-    <mergeCell ref="E254:F254"/>
-    <mergeCell ref="E255:F255"/>
-    <mergeCell ref="E256:F256"/>
-    <mergeCell ref="E235:F235"/>
-    <mergeCell ref="E236:F236"/>
-    <mergeCell ref="E237:F237"/>
-    <mergeCell ref="E238:F238"/>
-    <mergeCell ref="E239:F239"/>
-    <mergeCell ref="E240:F240"/>
-    <mergeCell ref="E241:F241"/>
-    <mergeCell ref="E242:F242"/>
-    <mergeCell ref="E243:F243"/>
-    <mergeCell ref="E244:F244"/>
-    <mergeCell ref="E245:F245"/>
-    <mergeCell ref="E246:F246"/>
-    <mergeCell ref="E247:F247"/>
-    <mergeCell ref="E248:F248"/>
-    <mergeCell ref="E249:F249"/>
-    <mergeCell ref="E250:F250"/>
-    <mergeCell ref="E251:F251"/>
-    <mergeCell ref="E362:F362"/>
-    <mergeCell ref="E363:F363"/>
-    <mergeCell ref="E304:F304"/>
-    <mergeCell ref="E305:F305"/>
-    <mergeCell ref="E306:F306"/>
-    <mergeCell ref="E307:F307"/>
-    <mergeCell ref="E308:F308"/>
-    <mergeCell ref="E309:F309"/>
-    <mergeCell ref="E310:F310"/>
-    <mergeCell ref="E311:F311"/>
-    <mergeCell ref="E312:F312"/>
-    <mergeCell ref="E313:F313"/>
-    <mergeCell ref="E314:F314"/>
-    <mergeCell ref="E315:F315"/>
-    <mergeCell ref="E316:F316"/>
-    <mergeCell ref="E317:F317"/>
-    <mergeCell ref="E318:F318"/>
-    <mergeCell ref="E319:F319"/>
-    <mergeCell ref="E320:F320"/>
-    <mergeCell ref="E321:F321"/>
-    <mergeCell ref="E322:F322"/>
-    <mergeCell ref="E323:F323"/>
-    <mergeCell ref="E324:F324"/>
-    <mergeCell ref="E325:F325"/>
-    <mergeCell ref="E364:F364"/>
-    <mergeCell ref="E365:F365"/>
-    <mergeCell ref="E366:F366"/>
-    <mergeCell ref="E367:F367"/>
-    <mergeCell ref="E368:F368"/>
-    <mergeCell ref="E369:F369"/>
-    <mergeCell ref="E370:F370"/>
-    <mergeCell ref="E371:F371"/>
-    <mergeCell ref="E327:F327"/>
-    <mergeCell ref="E328:F328"/>
-    <mergeCell ref="E329:F329"/>
-    <mergeCell ref="E330:F330"/>
-    <mergeCell ref="E331:F331"/>
-    <mergeCell ref="E332:F332"/>
-    <mergeCell ref="E333:F333"/>
-    <mergeCell ref="E390:F390"/>
-    <mergeCell ref="E391:F391"/>
-    <mergeCell ref="E334:F334"/>
-    <mergeCell ref="E335:F335"/>
-    <mergeCell ref="E336:F336"/>
-    <mergeCell ref="E337:F337"/>
-    <mergeCell ref="E338:F338"/>
-    <mergeCell ref="E339:F339"/>
-    <mergeCell ref="E340:F340"/>
-    <mergeCell ref="E341:F341"/>
-    <mergeCell ref="E342:F342"/>
-    <mergeCell ref="E343:F343"/>
-    <mergeCell ref="E344:F344"/>
-    <mergeCell ref="E345:F345"/>
-    <mergeCell ref="E346:F346"/>
-    <mergeCell ref="E347:F347"/>
-    <mergeCell ref="E348:F348"/>
-    <mergeCell ref="E392:F392"/>
-    <mergeCell ref="E393:F393"/>
-    <mergeCell ref="E394:F394"/>
-    <mergeCell ref="E350:F350"/>
-    <mergeCell ref="E351:F351"/>
-    <mergeCell ref="E352:F352"/>
-    <mergeCell ref="E353:F353"/>
-    <mergeCell ref="E354:F354"/>
-    <mergeCell ref="E355:F355"/>
-    <mergeCell ref="E356:F356"/>
-    <mergeCell ref="E357:F357"/>
-    <mergeCell ref="E358:F358"/>
-    <mergeCell ref="E359:F359"/>
-    <mergeCell ref="E360:F360"/>
-    <mergeCell ref="E361:F361"/>
-    <mergeCell ref="E373:F373"/>
-    <mergeCell ref="E374:F374"/>
-    <mergeCell ref="E375:F375"/>
-    <mergeCell ref="E376:F376"/>
-    <mergeCell ref="E377:F377"/>
-    <mergeCell ref="E378:F378"/>
-    <mergeCell ref="E379:F379"/>
-    <mergeCell ref="E380:F380"/>
-    <mergeCell ref="E381:F381"/>
-    <mergeCell ref="E382:F382"/>
-    <mergeCell ref="E383:F383"/>
-    <mergeCell ref="E384:F384"/>
-    <mergeCell ref="E385:F385"/>
-    <mergeCell ref="E386:F386"/>
-    <mergeCell ref="E387:F387"/>
-    <mergeCell ref="E388:F388"/>
-    <mergeCell ref="E389:F389"/>
-    <mergeCell ref="E416:F416"/>
-    <mergeCell ref="E414:F414"/>
-    <mergeCell ref="E412:F412"/>
-    <mergeCell ref="E410:F410"/>
-    <mergeCell ref="E408:F408"/>
-    <mergeCell ref="E406:F406"/>
-    <mergeCell ref="E404:F404"/>
-    <mergeCell ref="E402:F402"/>
-    <mergeCell ref="E400:F400"/>
-    <mergeCell ref="E398:F398"/>
-    <mergeCell ref="E396:F396"/>
-    <mergeCell ref="E1518:F1518"/>
-    <mergeCell ref="E1519:F1519"/>
-    <mergeCell ref="E1520:F1520"/>
-    <mergeCell ref="E1521:F1521"/>
-    <mergeCell ref="E1512:F1512"/>
-    <mergeCell ref="E1513:F1513"/>
-    <mergeCell ref="E1514:F1514"/>
-    <mergeCell ref="E1515:F1515"/>
-    <mergeCell ref="E1516:F1516"/>
-    <mergeCell ref="E1517:F1517"/>
-    <mergeCell ref="E1506:F1506"/>
-    <mergeCell ref="E1507:F1507"/>
-    <mergeCell ref="E1508:F1508"/>
-    <mergeCell ref="E1509:F1509"/>
-    <mergeCell ref="E1510:F1510"/>
-    <mergeCell ref="E1511:F1511"/>
-    <mergeCell ref="E1500:F1500"/>
-    <mergeCell ref="E1501:F1501"/>
-    <mergeCell ref="E1502:F1502"/>
-    <mergeCell ref="E1503:F1503"/>
-    <mergeCell ref="E1504:F1504"/>
-    <mergeCell ref="E1505:F1505"/>
-    <mergeCell ref="E1493:F1493"/>
-    <mergeCell ref="E1494:F1494"/>
-    <mergeCell ref="E1495:F1495"/>
-    <mergeCell ref="E1496:F1496"/>
-    <mergeCell ref="E1497:F1497"/>
-    <mergeCell ref="E1498:F1498"/>
-    <mergeCell ref="E1487:F1487"/>
-    <mergeCell ref="E1488:F1488"/>
-    <mergeCell ref="E1489:F1489"/>
-    <mergeCell ref="E1490:F1490"/>
-    <mergeCell ref="E1491:F1491"/>
-    <mergeCell ref="E1492:F1492"/>
-    <mergeCell ref="E1481:F1481"/>
-    <mergeCell ref="E1482:F1482"/>
-    <mergeCell ref="E1483:F1483"/>
-    <mergeCell ref="E1484:F1484"/>
-    <mergeCell ref="E1485:F1485"/>
-    <mergeCell ref="E1486:F1486"/>
-    <mergeCell ref="E1474:F1474"/>
-    <mergeCell ref="E1475:F1475"/>
-    <mergeCell ref="E1477:F1477"/>
-    <mergeCell ref="E1478:F1478"/>
-    <mergeCell ref="E1479:F1479"/>
-    <mergeCell ref="E1480:F1480"/>
-    <mergeCell ref="E1468:F1468"/>
-    <mergeCell ref="E1469:F1469"/>
-    <mergeCell ref="E1470:F1470"/>
-    <mergeCell ref="E1471:F1471"/>
-    <mergeCell ref="E1472:F1472"/>
-    <mergeCell ref="E1473:F1473"/>
-    <mergeCell ref="E1462:F1462"/>
-    <mergeCell ref="E1463:F1463"/>
-    <mergeCell ref="E1464:F1464"/>
-    <mergeCell ref="E1465:F1465"/>
-    <mergeCell ref="E1466:F1466"/>
-    <mergeCell ref="E1467:F1467"/>
-    <mergeCell ref="E1456:F1456"/>
-    <mergeCell ref="E1457:F1457"/>
-    <mergeCell ref="E1458:F1458"/>
-    <mergeCell ref="E1459:F1459"/>
-    <mergeCell ref="E1460:F1460"/>
-    <mergeCell ref="E1461:F1461"/>
-    <mergeCell ref="E1449:F1449"/>
-    <mergeCell ref="E1450:F1450"/>
-    <mergeCell ref="E1451:F1451"/>
-    <mergeCell ref="E1452:F1452"/>
-    <mergeCell ref="E1454:F1454"/>
-    <mergeCell ref="E1455:F1455"/>
-    <mergeCell ref="E1443:F1443"/>
-    <mergeCell ref="E1444:F1444"/>
-    <mergeCell ref="E1445:F1445"/>
-    <mergeCell ref="E1446:F1446"/>
-    <mergeCell ref="E1447:F1447"/>
-    <mergeCell ref="E1448:F1448"/>
-    <mergeCell ref="E1437:F1437"/>
-    <mergeCell ref="E1438:F1438"/>
-    <mergeCell ref="E1439:F1439"/>
-    <mergeCell ref="E1440:F1440"/>
-    <mergeCell ref="E1441:F1441"/>
-    <mergeCell ref="E1442:F1442"/>
-    <mergeCell ref="E1431:F1431"/>
-    <mergeCell ref="E1432:F1432"/>
-    <mergeCell ref="E1433:F1433"/>
-    <mergeCell ref="E1434:F1434"/>
-    <mergeCell ref="E1435:F1435"/>
-    <mergeCell ref="E1436:F1436"/>
-    <mergeCell ref="E1424:F1424"/>
-    <mergeCell ref="E1425:F1425"/>
-    <mergeCell ref="E1426:F1426"/>
-    <mergeCell ref="E1427:F1427"/>
-    <mergeCell ref="E1428:F1428"/>
-    <mergeCell ref="E1429:F1429"/>
-    <mergeCell ref="E1418:F1418"/>
-    <mergeCell ref="E1419:F1419"/>
-    <mergeCell ref="E1420:F1420"/>
-    <mergeCell ref="E1421:F1421"/>
-    <mergeCell ref="E1422:F1422"/>
-    <mergeCell ref="E1423:F1423"/>
-    <mergeCell ref="E1412:F1412"/>
-    <mergeCell ref="E1413:F1413"/>
-    <mergeCell ref="E1414:F1414"/>
-    <mergeCell ref="E1415:F1415"/>
-    <mergeCell ref="E1416:F1416"/>
-    <mergeCell ref="E1417:F1417"/>
-    <mergeCell ref="E1405:F1405"/>
-    <mergeCell ref="E1406:F1406"/>
-    <mergeCell ref="E1408:F1408"/>
-    <mergeCell ref="E1409:F1409"/>
-    <mergeCell ref="E1410:F1410"/>
-    <mergeCell ref="E1411:F1411"/>
-    <mergeCell ref="E1399:F1399"/>
-    <mergeCell ref="E1400:F1400"/>
-    <mergeCell ref="E1401:F1401"/>
-    <mergeCell ref="E1402:F1402"/>
-    <mergeCell ref="E1403:F1403"/>
-    <mergeCell ref="E1404:F1404"/>
-    <mergeCell ref="E1393:F1393"/>
-    <mergeCell ref="E1394:F1394"/>
-    <mergeCell ref="E1395:F1395"/>
-    <mergeCell ref="E1396:F1396"/>
-    <mergeCell ref="E1397:F1397"/>
-    <mergeCell ref="E1398:F1398"/>
-    <mergeCell ref="E1387:F1387"/>
-    <mergeCell ref="E1388:F1388"/>
-    <mergeCell ref="E1389:F1389"/>
-    <mergeCell ref="E1390:F1390"/>
-    <mergeCell ref="E1391:F1391"/>
-    <mergeCell ref="E1392:F1392"/>
-    <mergeCell ref="E1380:F1380"/>
-    <mergeCell ref="E1381:F1381"/>
-    <mergeCell ref="E1382:F1382"/>
-    <mergeCell ref="E1383:F1383"/>
-    <mergeCell ref="E1385:F1385"/>
-    <mergeCell ref="E1386:F1386"/>
-    <mergeCell ref="E1374:F1374"/>
-    <mergeCell ref="E1375:F1375"/>
-    <mergeCell ref="E1376:F1376"/>
-    <mergeCell ref="E1377:F1377"/>
-    <mergeCell ref="E1378:F1378"/>
-    <mergeCell ref="E1379:F1379"/>
-    <mergeCell ref="E1368:F1368"/>
-    <mergeCell ref="E1369:F1369"/>
-    <mergeCell ref="E1370:F1370"/>
-    <mergeCell ref="E1371:F1371"/>
-    <mergeCell ref="E1372:F1372"/>
-    <mergeCell ref="E1373:F1373"/>
-    <mergeCell ref="E1362:F1362"/>
-    <mergeCell ref="E1363:F1363"/>
-    <mergeCell ref="E1364:F1364"/>
-    <mergeCell ref="E1365:F1365"/>
-    <mergeCell ref="E1366:F1366"/>
-    <mergeCell ref="E1367:F1367"/>
-    <mergeCell ref="E1355:F1355"/>
-    <mergeCell ref="E1356:F1356"/>
-    <mergeCell ref="E1357:F1357"/>
-    <mergeCell ref="E1358:F1358"/>
-    <mergeCell ref="E1359:F1359"/>
-    <mergeCell ref="E1360:F1360"/>
-    <mergeCell ref="E1349:F1349"/>
-    <mergeCell ref="E1350:F1350"/>
-    <mergeCell ref="E1351:F1351"/>
-    <mergeCell ref="E1352:F1352"/>
-    <mergeCell ref="E1353:F1353"/>
-    <mergeCell ref="E1354:F1354"/>
-    <mergeCell ref="E1343:F1343"/>
-    <mergeCell ref="E1344:F1344"/>
-    <mergeCell ref="E1345:F1345"/>
-    <mergeCell ref="E1346:F1346"/>
-    <mergeCell ref="E1347:F1347"/>
-    <mergeCell ref="E1348:F1348"/>
-    <mergeCell ref="E1336:F1336"/>
-    <mergeCell ref="E1337:F1337"/>
-    <mergeCell ref="E1339:F1339"/>
-    <mergeCell ref="E1340:F1340"/>
-    <mergeCell ref="E1341:F1341"/>
-    <mergeCell ref="E1342:F1342"/>
-    <mergeCell ref="E1330:F1330"/>
-    <mergeCell ref="E1331:F1331"/>
-    <mergeCell ref="E1332:F1332"/>
-    <mergeCell ref="E1333:F1333"/>
-    <mergeCell ref="E1334:F1334"/>
-    <mergeCell ref="E1335:F1335"/>
-    <mergeCell ref="E1324:F1324"/>
-    <mergeCell ref="E1325:F1325"/>
-    <mergeCell ref="E1326:F1326"/>
-    <mergeCell ref="E1327:F1327"/>
-    <mergeCell ref="E1328:F1328"/>
-    <mergeCell ref="E1329:F1329"/>
-    <mergeCell ref="E1318:F1318"/>
-    <mergeCell ref="E1319:F1319"/>
-    <mergeCell ref="E1320:F1320"/>
-    <mergeCell ref="E1321:F1321"/>
-    <mergeCell ref="E1322:F1322"/>
-    <mergeCell ref="E1323:F1323"/>
-    <mergeCell ref="E1311:F1311"/>
-    <mergeCell ref="E1312:F1312"/>
-    <mergeCell ref="E1313:F1313"/>
-    <mergeCell ref="E1314:F1314"/>
-    <mergeCell ref="E1316:F1316"/>
-    <mergeCell ref="E1317:F1317"/>
-    <mergeCell ref="E1305:F1305"/>
-    <mergeCell ref="E1306:F1306"/>
-    <mergeCell ref="E1307:F1307"/>
-    <mergeCell ref="E1308:F1308"/>
-    <mergeCell ref="E1309:F1309"/>
-    <mergeCell ref="E1310:F1310"/>
-    <mergeCell ref="E1299:F1299"/>
-    <mergeCell ref="E1300:F1300"/>
-    <mergeCell ref="E1301:F1301"/>
-    <mergeCell ref="E1302:F1302"/>
-    <mergeCell ref="E1303:F1303"/>
-    <mergeCell ref="E1304:F1304"/>
-    <mergeCell ref="E1293:F1293"/>
-    <mergeCell ref="E1294:F1294"/>
-    <mergeCell ref="E1295:F1295"/>
-    <mergeCell ref="E1296:F1296"/>
-    <mergeCell ref="E1297:F1297"/>
-    <mergeCell ref="E1298:F1298"/>
-    <mergeCell ref="E1286:F1286"/>
-    <mergeCell ref="E1287:F1287"/>
-    <mergeCell ref="E1288:F1288"/>
-    <mergeCell ref="E1289:F1289"/>
-    <mergeCell ref="E1290:F1290"/>
-    <mergeCell ref="E1291:F1291"/>
-    <mergeCell ref="E1280:F1280"/>
-    <mergeCell ref="E1281:F1281"/>
-    <mergeCell ref="E1282:F1282"/>
-    <mergeCell ref="E1283:F1283"/>
-    <mergeCell ref="E1284:F1284"/>
-    <mergeCell ref="E1285:F1285"/>
-    <mergeCell ref="E1274:F1274"/>
-    <mergeCell ref="E1275:F1275"/>
-    <mergeCell ref="E1276:F1276"/>
-    <mergeCell ref="E1277:F1277"/>
-    <mergeCell ref="E1278:F1278"/>
-    <mergeCell ref="E1279:F1279"/>
-    <mergeCell ref="E1267:F1267"/>
-    <mergeCell ref="E1268:F1268"/>
-    <mergeCell ref="E1270:F1270"/>
-    <mergeCell ref="E1271:F1271"/>
-    <mergeCell ref="E1272:F1272"/>
-    <mergeCell ref="E1273:F1273"/>
-    <mergeCell ref="E1261:F1261"/>
-    <mergeCell ref="E1262:F1262"/>
-    <mergeCell ref="E1263:F1263"/>
-    <mergeCell ref="E1264:F1264"/>
-    <mergeCell ref="E1265:F1265"/>
-    <mergeCell ref="E1266:F1266"/>
-    <mergeCell ref="E1255:F1255"/>
-    <mergeCell ref="E1256:F1256"/>
-    <mergeCell ref="E1257:F1257"/>
-    <mergeCell ref="E1258:F1258"/>
-    <mergeCell ref="E1259:F1259"/>
-    <mergeCell ref="E1260:F1260"/>
-    <mergeCell ref="E1249:F1249"/>
-    <mergeCell ref="E1250:F1250"/>
-    <mergeCell ref="E1251:F1251"/>
-    <mergeCell ref="E1252:F1252"/>
-    <mergeCell ref="E1253:F1253"/>
-    <mergeCell ref="E1254:F1254"/>
-    <mergeCell ref="E1242:F1242"/>
-    <mergeCell ref="E1243:F1243"/>
-    <mergeCell ref="E1244:F1244"/>
-    <mergeCell ref="E1245:F1245"/>
-    <mergeCell ref="E1247:F1247"/>
-    <mergeCell ref="E1248:F1248"/>
-    <mergeCell ref="E1236:F1236"/>
-    <mergeCell ref="E1237:F1237"/>
-    <mergeCell ref="E1238:F1238"/>
-    <mergeCell ref="E1239:F1239"/>
-    <mergeCell ref="E1240:F1240"/>
-    <mergeCell ref="E1241:F1241"/>
-    <mergeCell ref="E1230:F1230"/>
-    <mergeCell ref="E1231:F1231"/>
-    <mergeCell ref="E1232:F1232"/>
-    <mergeCell ref="E1233:F1233"/>
-    <mergeCell ref="E1234:F1234"/>
-    <mergeCell ref="E1235:F1235"/>
-    <mergeCell ref="E1224:F1224"/>
-    <mergeCell ref="E1225:F1225"/>
-    <mergeCell ref="E1226:F1226"/>
-    <mergeCell ref="E1227:F1227"/>
-    <mergeCell ref="E1228:F1228"/>
-    <mergeCell ref="E1229:F1229"/>
-    <mergeCell ref="E1217:F1217"/>
-    <mergeCell ref="E1218:F1218"/>
-    <mergeCell ref="E1219:F1219"/>
-    <mergeCell ref="E1220:F1220"/>
-    <mergeCell ref="E1221:F1221"/>
-    <mergeCell ref="E1222:F1222"/>
-    <mergeCell ref="E1211:F1211"/>
-    <mergeCell ref="E1212:F1212"/>
-    <mergeCell ref="E1213:F1213"/>
-    <mergeCell ref="E1214:F1214"/>
-    <mergeCell ref="E1215:F1215"/>
-    <mergeCell ref="E1216:F1216"/>
-    <mergeCell ref="E1205:F1205"/>
-    <mergeCell ref="E1206:F1206"/>
-    <mergeCell ref="E1207:F1207"/>
-    <mergeCell ref="E1208:F1208"/>
-    <mergeCell ref="E1209:F1209"/>
-    <mergeCell ref="E1210:F1210"/>
-    <mergeCell ref="E1198:F1198"/>
-    <mergeCell ref="E1199:F1199"/>
-    <mergeCell ref="E1201:F1201"/>
-    <mergeCell ref="E1202:F1202"/>
-    <mergeCell ref="E1203:F1203"/>
-    <mergeCell ref="E1204:F1204"/>
-    <mergeCell ref="E1192:F1192"/>
-    <mergeCell ref="E1193:F1193"/>
-    <mergeCell ref="E1194:F1194"/>
-    <mergeCell ref="E1195:F1195"/>
-    <mergeCell ref="E1196:F1196"/>
-    <mergeCell ref="E1197:F1197"/>
-    <mergeCell ref="E1186:F1186"/>
-    <mergeCell ref="E1187:F1187"/>
-    <mergeCell ref="E1188:F1188"/>
-    <mergeCell ref="E1189:F1189"/>
-    <mergeCell ref="E1190:F1190"/>
-    <mergeCell ref="E1191:F1191"/>
-    <mergeCell ref="E1180:F1180"/>
-    <mergeCell ref="E1181:F1181"/>
-    <mergeCell ref="E1182:F1182"/>
-    <mergeCell ref="E1183:F1183"/>
-    <mergeCell ref="E1184:F1184"/>
-    <mergeCell ref="E1185:F1185"/>
-    <mergeCell ref="E1173:F1173"/>
-    <mergeCell ref="E1174:F1174"/>
-    <mergeCell ref="E1175:F1175"/>
-    <mergeCell ref="E1176:F1176"/>
-    <mergeCell ref="E1178:F1178"/>
-    <mergeCell ref="E1179:F1179"/>
-    <mergeCell ref="E1167:F1167"/>
-    <mergeCell ref="E1168:F1168"/>
-    <mergeCell ref="E1169:F1169"/>
-    <mergeCell ref="E1170:F1170"/>
-    <mergeCell ref="E1171:F1171"/>
-    <mergeCell ref="E1172:F1172"/>
-    <mergeCell ref="E1161:F1161"/>
-    <mergeCell ref="E1162:F1162"/>
-    <mergeCell ref="E1163:F1163"/>
-    <mergeCell ref="E1164:F1164"/>
-    <mergeCell ref="E1165:F1165"/>
-    <mergeCell ref="E1166:F1166"/>
-    <mergeCell ref="E1155:F1155"/>
-    <mergeCell ref="E1156:F1156"/>
-    <mergeCell ref="E1157:F1157"/>
-    <mergeCell ref="E1158:F1158"/>
-    <mergeCell ref="E1159:F1159"/>
-    <mergeCell ref="E1160:F1160"/>
-    <mergeCell ref="E1148:F1148"/>
-    <mergeCell ref="E1149:F1149"/>
-    <mergeCell ref="E1150:F1150"/>
-    <mergeCell ref="E1151:F1151"/>
-    <mergeCell ref="E1152:F1152"/>
-    <mergeCell ref="E1153:F1153"/>
-    <mergeCell ref="E1142:F1142"/>
-    <mergeCell ref="E1143:F1143"/>
-    <mergeCell ref="E1144:F1144"/>
-    <mergeCell ref="E1145:F1145"/>
-    <mergeCell ref="E1146:F1146"/>
-    <mergeCell ref="E1147:F1147"/>
-    <mergeCell ref="E1136:F1136"/>
-    <mergeCell ref="E1137:F1137"/>
-    <mergeCell ref="E1138:F1138"/>
-    <mergeCell ref="E1139:F1139"/>
-    <mergeCell ref="E1140:F1140"/>
-    <mergeCell ref="E1141:F1141"/>
-    <mergeCell ref="E1129:F1129"/>
-    <mergeCell ref="E1130:F1130"/>
-    <mergeCell ref="E1132:F1132"/>
-    <mergeCell ref="E1133:F1133"/>
-    <mergeCell ref="E1134:F1134"/>
-    <mergeCell ref="E1135:F1135"/>
-    <mergeCell ref="E1123:F1123"/>
-    <mergeCell ref="E1124:F1124"/>
-    <mergeCell ref="E1125:F1125"/>
-    <mergeCell ref="E1126:F1126"/>
-    <mergeCell ref="E1127:F1127"/>
-    <mergeCell ref="E1128:F1128"/>
-    <mergeCell ref="E1117:F1117"/>
-    <mergeCell ref="E1118:F1118"/>
-    <mergeCell ref="E1119:F1119"/>
-    <mergeCell ref="E1120:F1120"/>
-    <mergeCell ref="E1121:F1121"/>
-    <mergeCell ref="E1122:F1122"/>
-    <mergeCell ref="E1111:F1111"/>
-    <mergeCell ref="E1112:F1112"/>
-    <mergeCell ref="E1113:F1113"/>
-    <mergeCell ref="E1114:F1114"/>
-    <mergeCell ref="E1115:F1115"/>
-    <mergeCell ref="E1116:F1116"/>
-    <mergeCell ref="E1104:F1104"/>
-    <mergeCell ref="E1105:F1105"/>
-    <mergeCell ref="E1106:F1106"/>
-    <mergeCell ref="E1107:F1107"/>
-    <mergeCell ref="E1109:F1109"/>
-    <mergeCell ref="E1110:F1110"/>
-    <mergeCell ref="E1098:F1098"/>
-    <mergeCell ref="E1099:F1099"/>
-    <mergeCell ref="E1100:F1100"/>
-    <mergeCell ref="E1101:F1101"/>
-    <mergeCell ref="E1102:F1102"/>
-    <mergeCell ref="E1103:F1103"/>
-    <mergeCell ref="E1092:F1092"/>
-    <mergeCell ref="E1093:F1093"/>
-    <mergeCell ref="E1094:F1094"/>
-    <mergeCell ref="E1095:F1095"/>
-    <mergeCell ref="E1096:F1096"/>
-    <mergeCell ref="E1097:F1097"/>
-    <mergeCell ref="E1086:F1086"/>
-    <mergeCell ref="E1087:F1087"/>
-    <mergeCell ref="E1088:F1088"/>
-    <mergeCell ref="E1089:F1089"/>
-    <mergeCell ref="E1090:F1090"/>
-    <mergeCell ref="E1091:F1091"/>
-    <mergeCell ref="E1079:F1079"/>
-    <mergeCell ref="E1080:F1080"/>
-    <mergeCell ref="E1081:F1081"/>
-    <mergeCell ref="E1082:F1082"/>
-    <mergeCell ref="E1083:F1083"/>
-    <mergeCell ref="E1084:F1084"/>
-    <mergeCell ref="E1073:F1073"/>
-    <mergeCell ref="E1074:F1074"/>
-    <mergeCell ref="E1075:F1075"/>
-    <mergeCell ref="E1076:F1076"/>
-    <mergeCell ref="E1077:F1077"/>
-    <mergeCell ref="E1078:F1078"/>
-    <mergeCell ref="E1067:F1067"/>
-    <mergeCell ref="E1068:F1068"/>
-    <mergeCell ref="E1069:F1069"/>
-    <mergeCell ref="E1070:F1070"/>
-    <mergeCell ref="E1071:F1071"/>
-    <mergeCell ref="E1072:F1072"/>
-    <mergeCell ref="E1060:F1060"/>
-    <mergeCell ref="E1061:F1061"/>
-    <mergeCell ref="E1063:F1063"/>
-    <mergeCell ref="E1064:F1064"/>
-    <mergeCell ref="E1065:F1065"/>
-    <mergeCell ref="E1066:F1066"/>
-    <mergeCell ref="E1054:F1054"/>
-    <mergeCell ref="E1055:F1055"/>
-    <mergeCell ref="E1056:F1056"/>
-    <mergeCell ref="E1057:F1057"/>
-    <mergeCell ref="E1058:F1058"/>
-    <mergeCell ref="E1059:F1059"/>
-    <mergeCell ref="E1048:F1048"/>
-    <mergeCell ref="E1049:F1049"/>
-    <mergeCell ref="E1050:F1050"/>
-    <mergeCell ref="E1051:F1051"/>
-    <mergeCell ref="E1052:F1052"/>
-    <mergeCell ref="E1053:F1053"/>
-    <mergeCell ref="E1042:F1042"/>
-    <mergeCell ref="E1043:F1043"/>
-    <mergeCell ref="E1044:F1044"/>
-    <mergeCell ref="E1045:F1045"/>
-    <mergeCell ref="E1046:F1046"/>
-    <mergeCell ref="E1047:F1047"/>
-    <mergeCell ref="E1035:F1035"/>
-    <mergeCell ref="E1036:F1036"/>
-    <mergeCell ref="E1037:F1037"/>
-    <mergeCell ref="E1038:F1038"/>
-    <mergeCell ref="E1040:F1040"/>
-    <mergeCell ref="E1041:F1041"/>
-    <mergeCell ref="E1029:F1029"/>
-    <mergeCell ref="E1030:F1030"/>
-    <mergeCell ref="E1031:F1031"/>
-    <mergeCell ref="E1032:F1032"/>
-    <mergeCell ref="E1033:F1033"/>
-    <mergeCell ref="E1034:F1034"/>
-    <mergeCell ref="E1023:F1023"/>
-    <mergeCell ref="E1024:F1024"/>
-    <mergeCell ref="E1025:F1025"/>
-    <mergeCell ref="E1026:F1026"/>
-    <mergeCell ref="E1027:F1027"/>
-    <mergeCell ref="E1028:F1028"/>
-    <mergeCell ref="E1017:F1017"/>
-    <mergeCell ref="E1018:F1018"/>
-    <mergeCell ref="E1019:F1019"/>
-    <mergeCell ref="E1020:F1020"/>
-    <mergeCell ref="E1021:F1021"/>
-    <mergeCell ref="E1022:F1022"/>
-    <mergeCell ref="E1010:F1010"/>
-    <mergeCell ref="E1011:F1011"/>
-    <mergeCell ref="E1012:F1012"/>
-    <mergeCell ref="E1013:F1013"/>
-    <mergeCell ref="E1014:F1014"/>
-    <mergeCell ref="E1015:F1015"/>
-    <mergeCell ref="E1004:F1004"/>
-    <mergeCell ref="E1005:F1005"/>
-    <mergeCell ref="E1006:F1006"/>
-    <mergeCell ref="E1007:F1007"/>
-    <mergeCell ref="E1008:F1008"/>
-    <mergeCell ref="E1009:F1009"/>
-    <mergeCell ref="E998:F998"/>
-    <mergeCell ref="E999:F999"/>
-    <mergeCell ref="E1000:F1000"/>
-    <mergeCell ref="E1001:F1001"/>
-    <mergeCell ref="E1002:F1002"/>
-    <mergeCell ref="E1003:F1003"/>
-    <mergeCell ref="E991:F991"/>
-    <mergeCell ref="E992:F992"/>
-    <mergeCell ref="E994:F994"/>
-    <mergeCell ref="E995:F995"/>
-    <mergeCell ref="E996:F996"/>
-    <mergeCell ref="E997:F997"/>
-    <mergeCell ref="E985:F985"/>
-    <mergeCell ref="E986:F986"/>
-    <mergeCell ref="E987:F987"/>
-    <mergeCell ref="E988:F988"/>
-    <mergeCell ref="E989:F989"/>
-    <mergeCell ref="E990:F990"/>
-    <mergeCell ref="E979:F979"/>
-    <mergeCell ref="E980:F980"/>
-    <mergeCell ref="E981:F981"/>
-    <mergeCell ref="E982:F982"/>
-    <mergeCell ref="E983:F983"/>
-    <mergeCell ref="E984:F984"/>
-    <mergeCell ref="E971:F971"/>
-    <mergeCell ref="E972:F972"/>
-    <mergeCell ref="E973:F973"/>
-    <mergeCell ref="E974:F974"/>
-    <mergeCell ref="E975:F975"/>
-    <mergeCell ref="E976:F976"/>
-    <mergeCell ref="E977:F977"/>
-    <mergeCell ref="E978:F978"/>
-    <mergeCell ref="E966:F966"/>
-    <mergeCell ref="E967:F967"/>
-    <mergeCell ref="E968:F968"/>
-    <mergeCell ref="E969:F969"/>
-    <mergeCell ref="E960:F960"/>
-    <mergeCell ref="E961:F961"/>
-    <mergeCell ref="E962:F962"/>
-    <mergeCell ref="E963:F963"/>
-    <mergeCell ref="E964:F964"/>
-    <mergeCell ref="E965:F965"/>
-    <mergeCell ref="E954:F954"/>
-    <mergeCell ref="E955:F955"/>
-    <mergeCell ref="E956:F956"/>
-    <mergeCell ref="E957:F957"/>
-    <mergeCell ref="E958:F958"/>
-    <mergeCell ref="E959:F959"/>
-    <mergeCell ref="E948:F948"/>
-    <mergeCell ref="E949:F949"/>
-    <mergeCell ref="E950:F950"/>
-    <mergeCell ref="E951:F951"/>
-    <mergeCell ref="E952:F952"/>
-    <mergeCell ref="E953:F953"/>
-    <mergeCell ref="E941:F941"/>
-    <mergeCell ref="E942:F942"/>
-    <mergeCell ref="E943:F943"/>
-    <mergeCell ref="E944:F944"/>
-    <mergeCell ref="E945:F945"/>
-    <mergeCell ref="E946:F946"/>
-    <mergeCell ref="E935:F935"/>
-    <mergeCell ref="E936:F936"/>
-    <mergeCell ref="E937:F937"/>
-    <mergeCell ref="E938:F938"/>
-    <mergeCell ref="E939:F939"/>
-    <mergeCell ref="E940:F940"/>
-    <mergeCell ref="E929:F929"/>
-    <mergeCell ref="E930:F930"/>
-    <mergeCell ref="E931:F931"/>
-    <mergeCell ref="E932:F932"/>
-    <mergeCell ref="E933:F933"/>
-    <mergeCell ref="E934:F934"/>
-    <mergeCell ref="E922:F922"/>
-    <mergeCell ref="E923:F923"/>
-    <mergeCell ref="E925:F925"/>
-    <mergeCell ref="E926:F926"/>
-    <mergeCell ref="E927:F927"/>
-    <mergeCell ref="E928:F928"/>
-    <mergeCell ref="E916:F916"/>
-    <mergeCell ref="E917:F917"/>
-    <mergeCell ref="E918:F918"/>
-    <mergeCell ref="E919:F919"/>
-    <mergeCell ref="E920:F920"/>
-    <mergeCell ref="E921:F921"/>
-    <mergeCell ref="E910:F910"/>
-    <mergeCell ref="E911:F911"/>
-    <mergeCell ref="E912:F912"/>
-    <mergeCell ref="E913:F913"/>
-    <mergeCell ref="E914:F914"/>
-    <mergeCell ref="E915:F915"/>
-    <mergeCell ref="E904:F904"/>
-    <mergeCell ref="E905:F905"/>
-    <mergeCell ref="E906:F906"/>
-    <mergeCell ref="E907:F907"/>
-    <mergeCell ref="E908:F908"/>
-    <mergeCell ref="E909:F909"/>
-    <mergeCell ref="E897:F897"/>
-    <mergeCell ref="E898:F898"/>
-    <mergeCell ref="E899:F899"/>
-    <mergeCell ref="E900:F900"/>
-    <mergeCell ref="E902:F902"/>
-    <mergeCell ref="E903:F903"/>
-    <mergeCell ref="E891:F891"/>
-    <mergeCell ref="E892:F892"/>
-    <mergeCell ref="E893:F893"/>
-    <mergeCell ref="E894:F894"/>
-    <mergeCell ref="E895:F895"/>
-    <mergeCell ref="E896:F896"/>
-    <mergeCell ref="E885:F885"/>
-    <mergeCell ref="E886:F886"/>
-    <mergeCell ref="E887:F887"/>
-    <mergeCell ref="E888:F888"/>
-    <mergeCell ref="E889:F889"/>
-    <mergeCell ref="E890:F890"/>
-    <mergeCell ref="E879:F879"/>
-    <mergeCell ref="E880:F880"/>
-    <mergeCell ref="E881:F881"/>
-    <mergeCell ref="E882:F882"/>
-    <mergeCell ref="E883:F883"/>
-    <mergeCell ref="E884:F884"/>
-    <mergeCell ref="E872:F872"/>
-    <mergeCell ref="E873:F873"/>
-    <mergeCell ref="E874:F874"/>
-    <mergeCell ref="E875:F875"/>
-    <mergeCell ref="E876:F876"/>
-    <mergeCell ref="E877:F877"/>
-    <mergeCell ref="E866:F866"/>
-    <mergeCell ref="E867:F867"/>
-    <mergeCell ref="E868:F868"/>
-    <mergeCell ref="E869:F869"/>
-    <mergeCell ref="E870:F870"/>
-    <mergeCell ref="E871:F871"/>
-    <mergeCell ref="E860:F860"/>
-    <mergeCell ref="E861:F861"/>
-    <mergeCell ref="E862:F862"/>
-    <mergeCell ref="E863:F863"/>
-    <mergeCell ref="E864:F864"/>
-    <mergeCell ref="E865:F865"/>
-    <mergeCell ref="E853:F853"/>
-    <mergeCell ref="E854:F854"/>
-    <mergeCell ref="E856:F856"/>
-    <mergeCell ref="E857:F857"/>
-    <mergeCell ref="E858:F858"/>
-    <mergeCell ref="E859:F859"/>
-    <mergeCell ref="E847:F847"/>
-    <mergeCell ref="E848:F848"/>
-    <mergeCell ref="E849:F849"/>
-    <mergeCell ref="E850:F850"/>
-    <mergeCell ref="E851:F851"/>
-    <mergeCell ref="E852:F852"/>
-    <mergeCell ref="E841:F841"/>
-    <mergeCell ref="E842:F842"/>
-    <mergeCell ref="E843:F843"/>
-    <mergeCell ref="E844:F844"/>
-    <mergeCell ref="E845:F845"/>
-    <mergeCell ref="E846:F846"/>
-    <mergeCell ref="E835:F835"/>
-    <mergeCell ref="E836:F836"/>
-    <mergeCell ref="E837:F837"/>
-    <mergeCell ref="E838:F838"/>
-    <mergeCell ref="E839:F839"/>
-    <mergeCell ref="E840:F840"/>
-    <mergeCell ref="E828:F828"/>
-    <mergeCell ref="E829:F829"/>
-    <mergeCell ref="E830:F830"/>
-    <mergeCell ref="E831:F831"/>
-    <mergeCell ref="E833:F833"/>
-    <mergeCell ref="E834:F834"/>
-    <mergeCell ref="E822:F822"/>
-    <mergeCell ref="E823:F823"/>
-    <mergeCell ref="E824:F824"/>
-    <mergeCell ref="E825:F825"/>
-    <mergeCell ref="E826:F826"/>
-    <mergeCell ref="E827:F827"/>
-    <mergeCell ref="E816:F816"/>
-    <mergeCell ref="E817:F817"/>
-    <mergeCell ref="E818:F818"/>
-    <mergeCell ref="E819:F819"/>
-    <mergeCell ref="E820:F820"/>
-    <mergeCell ref="E821:F821"/>
-    <mergeCell ref="E810:F810"/>
-    <mergeCell ref="E811:F811"/>
-    <mergeCell ref="E812:F812"/>
-    <mergeCell ref="E813:F813"/>
-    <mergeCell ref="E814:F814"/>
-    <mergeCell ref="E815:F815"/>
-    <mergeCell ref="E803:F803"/>
-    <mergeCell ref="E804:F804"/>
-    <mergeCell ref="E805:F805"/>
-    <mergeCell ref="E806:F806"/>
-    <mergeCell ref="E807:F807"/>
-    <mergeCell ref="E808:F808"/>
-    <mergeCell ref="E797:F797"/>
-    <mergeCell ref="E798:F798"/>
-    <mergeCell ref="E799:F799"/>
-    <mergeCell ref="E800:F800"/>
-    <mergeCell ref="E801:F801"/>
-    <mergeCell ref="E802:F802"/>
-    <mergeCell ref="E791:F791"/>
-    <mergeCell ref="E792:F792"/>
-    <mergeCell ref="E793:F793"/>
-    <mergeCell ref="E794:F794"/>
-    <mergeCell ref="E795:F795"/>
-    <mergeCell ref="E796:F796"/>
-    <mergeCell ref="E784:F784"/>
-    <mergeCell ref="E785:F785"/>
-    <mergeCell ref="E787:F787"/>
-    <mergeCell ref="E788:F788"/>
-    <mergeCell ref="E789:F789"/>
-    <mergeCell ref="E790:F790"/>
-    <mergeCell ref="E778:F778"/>
-    <mergeCell ref="E779:F779"/>
-    <mergeCell ref="E780:F780"/>
-    <mergeCell ref="E781:F781"/>
-    <mergeCell ref="E782:F782"/>
-    <mergeCell ref="E783:F783"/>
-    <mergeCell ref="E772:F772"/>
-    <mergeCell ref="E773:F773"/>
-    <mergeCell ref="E774:F774"/>
-    <mergeCell ref="E775:F775"/>
-    <mergeCell ref="E776:F776"/>
-    <mergeCell ref="E777:F777"/>
-    <mergeCell ref="E766:F766"/>
-    <mergeCell ref="E767:F767"/>
-    <mergeCell ref="E768:F768"/>
-    <mergeCell ref="E769:F769"/>
-    <mergeCell ref="E770:F770"/>
-    <mergeCell ref="E771:F771"/>
-    <mergeCell ref="E759:F759"/>
-    <mergeCell ref="E760:F760"/>
-    <mergeCell ref="E761:F761"/>
-    <mergeCell ref="E762:F762"/>
-    <mergeCell ref="E764:F764"/>
-    <mergeCell ref="E765:F765"/>
-    <mergeCell ref="E753:F753"/>
-    <mergeCell ref="E754:F754"/>
-    <mergeCell ref="E755:F755"/>
-    <mergeCell ref="E756:F756"/>
-    <mergeCell ref="E757:F757"/>
-    <mergeCell ref="E758:F758"/>
-    <mergeCell ref="E747:F747"/>
-    <mergeCell ref="E748:F748"/>
-    <mergeCell ref="E749:F749"/>
-    <mergeCell ref="E750:F750"/>
-    <mergeCell ref="E751:F751"/>
-    <mergeCell ref="E752:F752"/>
-    <mergeCell ref="E741:F741"/>
-    <mergeCell ref="E742:F742"/>
-    <mergeCell ref="E743:F743"/>
-    <mergeCell ref="E744:F744"/>
-    <mergeCell ref="E745:F745"/>
-    <mergeCell ref="E746:F746"/>
-    <mergeCell ref="E734:F734"/>
-    <mergeCell ref="E735:F735"/>
-    <mergeCell ref="E736:F736"/>
-    <mergeCell ref="E737:F737"/>
-    <mergeCell ref="E738:F738"/>
-    <mergeCell ref="E739:F739"/>
-    <mergeCell ref="E728:F728"/>
-    <mergeCell ref="E729:F729"/>
-    <mergeCell ref="E730:F730"/>
-    <mergeCell ref="E731:F731"/>
-    <mergeCell ref="E732:F732"/>
-    <mergeCell ref="E733:F733"/>
-    <mergeCell ref="E722:F722"/>
-    <mergeCell ref="E723:F723"/>
-    <mergeCell ref="E724:F724"/>
-    <mergeCell ref="E725:F725"/>
-    <mergeCell ref="E726:F726"/>
-    <mergeCell ref="E727:F727"/>
-    <mergeCell ref="E715:F715"/>
-    <mergeCell ref="E716:F716"/>
-    <mergeCell ref="E718:F718"/>
-    <mergeCell ref="E719:F719"/>
-    <mergeCell ref="E720:F720"/>
-    <mergeCell ref="E721:F721"/>
-    <mergeCell ref="E709:F709"/>
-    <mergeCell ref="E710:F710"/>
-    <mergeCell ref="E711:F711"/>
-    <mergeCell ref="E712:F712"/>
-    <mergeCell ref="E713:F713"/>
-    <mergeCell ref="E714:F714"/>
-    <mergeCell ref="E703:F703"/>
-    <mergeCell ref="E704:F704"/>
-    <mergeCell ref="E705:F705"/>
-    <mergeCell ref="E706:F706"/>
-    <mergeCell ref="E707:F707"/>
-    <mergeCell ref="E708:F708"/>
-    <mergeCell ref="E697:F697"/>
-    <mergeCell ref="E698:F698"/>
-    <mergeCell ref="E699:F699"/>
-    <mergeCell ref="E700:F700"/>
-    <mergeCell ref="E701:F701"/>
-    <mergeCell ref="E702:F702"/>
-    <mergeCell ref="E690:F690"/>
-    <mergeCell ref="E691:F691"/>
-    <mergeCell ref="E692:F692"/>
-    <mergeCell ref="E693:F693"/>
-    <mergeCell ref="E695:F695"/>
-    <mergeCell ref="E696:F696"/>
-    <mergeCell ref="E684:F684"/>
-    <mergeCell ref="E685:F685"/>
-    <mergeCell ref="E686:F686"/>
-    <mergeCell ref="E687:F687"/>
-    <mergeCell ref="E688:F688"/>
-    <mergeCell ref="E689:F689"/>
-    <mergeCell ref="E678:F678"/>
-    <mergeCell ref="E679:F679"/>
-    <mergeCell ref="E680:F680"/>
-    <mergeCell ref="E681:F681"/>
-    <mergeCell ref="E682:F682"/>
-    <mergeCell ref="E683:F683"/>
-    <mergeCell ref="E672:F672"/>
-    <mergeCell ref="E673:F673"/>
-    <mergeCell ref="E674:F674"/>
-    <mergeCell ref="E675:F675"/>
-    <mergeCell ref="E676:F676"/>
-    <mergeCell ref="E677:F677"/>
-    <mergeCell ref="E665:F665"/>
-    <mergeCell ref="E666:F666"/>
-    <mergeCell ref="E667:F667"/>
-    <mergeCell ref="E668:F668"/>
-    <mergeCell ref="E669:F669"/>
-    <mergeCell ref="E670:F670"/>
-    <mergeCell ref="E659:F659"/>
-    <mergeCell ref="E660:F660"/>
-    <mergeCell ref="E661:F661"/>
-    <mergeCell ref="E662:F662"/>
-    <mergeCell ref="E663:F663"/>
-    <mergeCell ref="E664:F664"/>
-    <mergeCell ref="E653:F653"/>
-    <mergeCell ref="E654:F654"/>
-    <mergeCell ref="E655:F655"/>
-    <mergeCell ref="E656:F656"/>
-    <mergeCell ref="E657:F657"/>
-    <mergeCell ref="E658:F658"/>
-    <mergeCell ref="E646:F646"/>
-    <mergeCell ref="E647:F647"/>
-    <mergeCell ref="E649:F649"/>
-    <mergeCell ref="E650:F650"/>
-    <mergeCell ref="E651:F651"/>
-    <mergeCell ref="E652:F652"/>
-    <mergeCell ref="E640:F640"/>
-    <mergeCell ref="E641:F641"/>
-    <mergeCell ref="E642:F642"/>
-    <mergeCell ref="E643:F643"/>
-    <mergeCell ref="E644:F644"/>
-    <mergeCell ref="E645:F645"/>
-    <mergeCell ref="E634:F634"/>
-    <mergeCell ref="E635:F635"/>
-    <mergeCell ref="E636:F636"/>
-    <mergeCell ref="E637:F637"/>
-    <mergeCell ref="E638:F638"/>
-    <mergeCell ref="E639:F639"/>
-    <mergeCell ref="E628:F628"/>
-    <mergeCell ref="E629:F629"/>
-    <mergeCell ref="E630:F630"/>
-    <mergeCell ref="E631:F631"/>
-    <mergeCell ref="E632:F632"/>
-    <mergeCell ref="E633:F633"/>
-    <mergeCell ref="E621:F621"/>
-    <mergeCell ref="E622:F622"/>
-    <mergeCell ref="E623:F623"/>
-    <mergeCell ref="E624:F624"/>
-    <mergeCell ref="E626:F626"/>
-    <mergeCell ref="E627:F627"/>
-    <mergeCell ref="E615:F615"/>
-    <mergeCell ref="E616:F616"/>
-    <mergeCell ref="E617:F617"/>
-    <mergeCell ref="E618:F618"/>
-    <mergeCell ref="E619:F619"/>
-    <mergeCell ref="E620:F620"/>
-    <mergeCell ref="E609:F609"/>
-    <mergeCell ref="E610:F610"/>
-    <mergeCell ref="E611:F611"/>
-    <mergeCell ref="E612:F612"/>
-    <mergeCell ref="E613:F613"/>
-    <mergeCell ref="E614:F614"/>
-    <mergeCell ref="E603:F603"/>
-    <mergeCell ref="E604:F604"/>
-    <mergeCell ref="E605:F605"/>
-    <mergeCell ref="E606:F606"/>
-    <mergeCell ref="E607:F607"/>
-    <mergeCell ref="E608:F608"/>
-    <mergeCell ref="E596:F596"/>
-    <mergeCell ref="E597:F597"/>
-    <mergeCell ref="E598:F598"/>
-    <mergeCell ref="E599:F599"/>
-    <mergeCell ref="E600:F600"/>
-    <mergeCell ref="E601:F601"/>
-    <mergeCell ref="E590:F590"/>
-    <mergeCell ref="E591:F591"/>
-    <mergeCell ref="E592:F592"/>
-    <mergeCell ref="E593:F593"/>
-    <mergeCell ref="E594:F594"/>
-    <mergeCell ref="E595:F595"/>
-    <mergeCell ref="E584:F584"/>
-    <mergeCell ref="E585:F585"/>
-    <mergeCell ref="E586:F586"/>
-    <mergeCell ref="E587:F587"/>
-    <mergeCell ref="E588:F588"/>
-    <mergeCell ref="E589:F589"/>
-    <mergeCell ref="E577:F577"/>
-    <mergeCell ref="E578:F578"/>
-    <mergeCell ref="E580:F580"/>
-    <mergeCell ref="E581:F581"/>
-    <mergeCell ref="E582:F582"/>
-    <mergeCell ref="E583:F583"/>
-    <mergeCell ref="E571:F571"/>
-    <mergeCell ref="E572:F572"/>
-    <mergeCell ref="E573:F573"/>
-    <mergeCell ref="E574:F574"/>
-    <mergeCell ref="E575:F575"/>
-    <mergeCell ref="E576:F576"/>
-    <mergeCell ref="E565:F565"/>
-    <mergeCell ref="E566:F566"/>
-    <mergeCell ref="E567:F567"/>
-    <mergeCell ref="E568:F568"/>
-    <mergeCell ref="E569:F569"/>
-    <mergeCell ref="E570:F570"/>
-    <mergeCell ref="E559:F559"/>
-    <mergeCell ref="E560:F560"/>
-    <mergeCell ref="E561:F561"/>
-    <mergeCell ref="E562:F562"/>
-    <mergeCell ref="E563:F563"/>
-    <mergeCell ref="E564:F564"/>
-    <mergeCell ref="E553:F553"/>
-    <mergeCell ref="E554:F554"/>
-    <mergeCell ref="E555:F555"/>
-    <mergeCell ref="E557:F557"/>
-    <mergeCell ref="E558:F558"/>
-    <mergeCell ref="E547:F547"/>
-    <mergeCell ref="E548:F548"/>
-    <mergeCell ref="E549:F549"/>
-    <mergeCell ref="E550:F550"/>
-    <mergeCell ref="E551:F551"/>
-    <mergeCell ref="E552:F552"/>
-    <mergeCell ref="E541:F541"/>
-    <mergeCell ref="E542:F542"/>
-    <mergeCell ref="E543:F543"/>
-    <mergeCell ref="E544:F544"/>
-    <mergeCell ref="E545:F545"/>
-    <mergeCell ref="E546:F546"/>
-    <mergeCell ref="E535:F535"/>
-    <mergeCell ref="E536:F536"/>
-    <mergeCell ref="E537:F537"/>
-    <mergeCell ref="E538:F538"/>
-    <mergeCell ref="E539:F539"/>
-    <mergeCell ref="E540:F540"/>
-    <mergeCell ref="E528:F528"/>
-    <mergeCell ref="E529:F529"/>
-    <mergeCell ref="E530:F530"/>
-    <mergeCell ref="E531:F531"/>
-    <mergeCell ref="E532:F532"/>
-    <mergeCell ref="E534:F534"/>
-    <mergeCell ref="E522:F522"/>
-    <mergeCell ref="E523:F523"/>
-    <mergeCell ref="E524:F524"/>
-    <mergeCell ref="E525:F525"/>
-    <mergeCell ref="E526:F526"/>
-    <mergeCell ref="E527:F527"/>
-    <mergeCell ref="E516:F516"/>
-    <mergeCell ref="E517:F517"/>
-    <mergeCell ref="E518:F518"/>
-    <mergeCell ref="E519:F519"/>
-    <mergeCell ref="E520:F520"/>
-    <mergeCell ref="E521:F521"/>
-    <mergeCell ref="E509:F509"/>
-    <mergeCell ref="E511:F511"/>
-    <mergeCell ref="E512:F512"/>
-    <mergeCell ref="E513:F513"/>
-    <mergeCell ref="E514:F514"/>
-    <mergeCell ref="E515:F515"/>
-    <mergeCell ref="E503:F503"/>
-    <mergeCell ref="E504:F504"/>
-    <mergeCell ref="E505:F505"/>
-    <mergeCell ref="E506:F506"/>
-    <mergeCell ref="E507:F507"/>
-    <mergeCell ref="E508:F508"/>
-    <mergeCell ref="E497:F497"/>
-    <mergeCell ref="E498:F498"/>
-    <mergeCell ref="E499:F499"/>
-    <mergeCell ref="E500:F500"/>
-    <mergeCell ref="E501:F501"/>
-    <mergeCell ref="E502:F502"/>
-    <mergeCell ref="E491:F491"/>
-    <mergeCell ref="E492:F492"/>
-    <mergeCell ref="E493:F493"/>
-    <mergeCell ref="E494:F494"/>
-    <mergeCell ref="E495:F495"/>
-    <mergeCell ref="E496:F496"/>
-    <mergeCell ref="E484:F484"/>
-    <mergeCell ref="E485:F485"/>
-    <mergeCell ref="E486:F486"/>
-    <mergeCell ref="E488:F488"/>
-    <mergeCell ref="E489:F489"/>
-    <mergeCell ref="E490:F490"/>
-    <mergeCell ref="E478:F478"/>
-    <mergeCell ref="E479:F479"/>
-    <mergeCell ref="E480:F480"/>
-    <mergeCell ref="E481:F481"/>
-    <mergeCell ref="E482:F482"/>
-    <mergeCell ref="E483:F483"/>
-    <mergeCell ref="E472:F472"/>
-    <mergeCell ref="E473:F473"/>
-    <mergeCell ref="E474:F474"/>
-    <mergeCell ref="E475:F475"/>
-    <mergeCell ref="E476:F476"/>
-    <mergeCell ref="E477:F477"/>
-    <mergeCell ref="E466:F466"/>
-    <mergeCell ref="E467:F467"/>
-    <mergeCell ref="E468:F468"/>
-    <mergeCell ref="E469:F469"/>
-    <mergeCell ref="E470:F470"/>
-    <mergeCell ref="E471:F471"/>
-    <mergeCell ref="E459:F459"/>
-    <mergeCell ref="E460:F460"/>
-    <mergeCell ref="E461:F461"/>
-    <mergeCell ref="E462:F462"/>
-    <mergeCell ref="E463:F463"/>
-    <mergeCell ref="E465:F465"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E442:F442"/>
-    <mergeCell ref="E443:F443"/>
-    <mergeCell ref="E444:F444"/>
-    <mergeCell ref="E445:F445"/>
-    <mergeCell ref="E446:F446"/>
-    <mergeCell ref="E419:F419"/>
-    <mergeCell ref="E420:F420"/>
-    <mergeCell ref="E421:F421"/>
-    <mergeCell ref="E422:F422"/>
-    <mergeCell ref="E423:F423"/>
-    <mergeCell ref="E424:F424"/>
-    <mergeCell ref="E425:F425"/>
-    <mergeCell ref="E426:F426"/>
-    <mergeCell ref="E427:F427"/>
-    <mergeCell ref="E428:F428"/>
-    <mergeCell ref="E429:F429"/>
-    <mergeCell ref="E430:F430"/>
-    <mergeCell ref="E431:F431"/>
-    <mergeCell ref="E432:F432"/>
-    <mergeCell ref="E397:F397"/>
-    <mergeCell ref="E399:F399"/>
-    <mergeCell ref="E401:F401"/>
-    <mergeCell ref="E403:F403"/>
-    <mergeCell ref="E405:F405"/>
-    <mergeCell ref="E407:F407"/>
-    <mergeCell ref="E409:F409"/>
-    <mergeCell ref="E411:F411"/>
-    <mergeCell ref="E413:F413"/>
-    <mergeCell ref="E415:F415"/>
-    <mergeCell ref="E417:F417"/>
-    <mergeCell ref="E433:F433"/>
-    <mergeCell ref="E434:F434"/>
-    <mergeCell ref="E435:F435"/>
-    <mergeCell ref="E436:F436"/>
-    <mergeCell ref="E437:F437"/>
-    <mergeCell ref="E438:F438"/>
-    <mergeCell ref="E439:F439"/>
-    <mergeCell ref="E440:F440"/>
-    <mergeCell ref="E453:F453"/>
-    <mergeCell ref="E454:F454"/>
-    <mergeCell ref="E455:F455"/>
-    <mergeCell ref="E456:F456"/>
-    <mergeCell ref="E457:F457"/>
-    <mergeCell ref="E458:F458"/>
-    <mergeCell ref="E447:F447"/>
-    <mergeCell ref="E448:F448"/>
-    <mergeCell ref="E449:F449"/>
-    <mergeCell ref="E450:F450"/>
-    <mergeCell ref="E451:F451"/>
-    <mergeCell ref="E452:F452"/>
-    <mergeCell ref="E298:F298"/>
-    <mergeCell ref="E299:F299"/>
-    <mergeCell ref="E300:F300"/>
-    <mergeCell ref="E301:F301"/>
-    <mergeCell ref="E302:F302"/>
-    <mergeCell ref="E281:F281"/>
-    <mergeCell ref="E282:F282"/>
-    <mergeCell ref="E283:F283"/>
-    <mergeCell ref="E284:F284"/>
-    <mergeCell ref="E285:F285"/>
-    <mergeCell ref="E286:F286"/>
-    <mergeCell ref="E287:F287"/>
-    <mergeCell ref="E288:F288"/>
-    <mergeCell ref="E289:F289"/>
-    <mergeCell ref="E290:F290"/>
-    <mergeCell ref="E291:F291"/>
-    <mergeCell ref="E292:F292"/>
-    <mergeCell ref="E293:F293"/>
-    <mergeCell ref="E294:F294"/>
-    <mergeCell ref="E295:F295"/>
-    <mergeCell ref="E296:F296"/>
-    <mergeCell ref="E297:F297"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="E139:F139"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="E120:F120"/>
-    <mergeCell ref="E121:F121"/>
-    <mergeCell ref="E122:F122"/>
-    <mergeCell ref="E123:F123"/>
-    <mergeCell ref="E124:F124"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E206:F206"/>
+    <mergeCell ref="E207:F207"/>
+    <mergeCell ref="E208:F208"/>
+    <mergeCell ref="E209:F209"/>
+    <mergeCell ref="E210:F210"/>
+    <mergeCell ref="E189:F189"/>
+    <mergeCell ref="E190:F190"/>
+    <mergeCell ref="E191:F191"/>
+    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="E193:F193"/>
+    <mergeCell ref="E194:F194"/>
+    <mergeCell ref="E195:F195"/>
+    <mergeCell ref="E196:F196"/>
+    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="E198:F198"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="E200:F200"/>
+    <mergeCell ref="E201:F201"/>
+    <mergeCell ref="E202:F202"/>
+    <mergeCell ref="E203:F203"/>
+    <mergeCell ref="E204:F204"/>
+    <mergeCell ref="E205:F205"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="E146:F146"/>
+    <mergeCell ref="E147:F147"/>
+    <mergeCell ref="E148:F148"/>
+    <mergeCell ref="E149:F149"/>
+    <mergeCell ref="E150:F150"/>
+    <mergeCell ref="E151:F151"/>
+    <mergeCell ref="E152:F152"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="E156:F156"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="E178:F178"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="E181:F181"/>
+    <mergeCell ref="E182:F182"/>
+    <mergeCell ref="E183:F183"/>
+    <mergeCell ref="E184:F184"/>
+    <mergeCell ref="E185:F185"/>
+    <mergeCell ref="E186:F186"/>
+    <mergeCell ref="E187:F187"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="E173:F173"/>
+    <mergeCell ref="E174:F174"/>
+    <mergeCell ref="E175:F175"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="E177:F177"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
